--- a/ETAT_CLIENTS_2026.xlsx
+++ b/ETAT_CLIENTS_2026.xlsx
@@ -4842,7 +4842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H279"/>
+  <dimension ref="A2:H281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5387,7 +5387,7 @@
         <v>437400.04</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>0</v>
+        <v>437400</v>
       </c>
       <c r="H17" s="8">
         <f>E17+F17-G17</f>
@@ -6657,12 +6657,12 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>C118</t>
+          <t>C1104</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>ABDOUNE RAFIK</t>
+          <t>AFIA FATSAH</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
@@ -6676,13 +6676,13 @@
         </is>
       </c>
       <c r="E54" s="8" t="n">
-        <v>700700</v>
+        <v>0</v>
       </c>
       <c r="F54" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>0</v>
+        <v>1183700</v>
       </c>
       <c r="H54" s="8">
         <f>E54+F54-G54</f>
@@ -6692,12 +6692,12 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>C132</t>
+          <t>C1105</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>SARL POULINA</t>
+          <t>DJAMRI ABD EL HAK</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="E55" s="8" t="n">
-        <v>42305.99</v>
+        <v>0</v>
       </c>
       <c r="F55" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>0</v>
+        <v>2851200</v>
       </c>
       <c r="H55" s="8">
         <f>E55+F55-G55</f>
@@ -6727,12 +6727,12 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>C136</t>
+          <t>C118</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>RENOFLEX</t>
+          <t>ABDOUNE RAFIK</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="E56" s="8" t="n">
-        <v>152000</v>
+        <v>700700</v>
       </c>
       <c r="F56" s="8" t="n">
         <v>0</v>
@@ -6762,12 +6762,12 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>C137</t>
+          <t>C132</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>BERKANI KHELAF</t>
+          <t>SARL POULINA</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -6781,13 +6781,13 @@
         </is>
       </c>
       <c r="E57" s="8" t="n">
-        <v>0</v>
+        <v>42305.99</v>
       </c>
       <c r="F57" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="8" t="n">
-        <v>160000.06</v>
+        <v>0</v>
       </c>
       <c r="H57" s="8">
         <f>E57+F57-G57</f>
@@ -6797,12 +6797,12 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>C164</t>
+          <t>C136</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>ETS DJENNADI REYAD</t>
+          <t>RENOFLEX</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="E58" s="8" t="n">
-        <v>-4500000</v>
+        <v>152000</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>2441390.87</v>
+        <v>0</v>
       </c>
       <c r="G58" s="8" t="n">
         <v>0</v>
@@ -6832,12 +6832,12 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>C174</t>
+          <t>C137</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>HAMMAOUI LAHDI</t>
+          <t>BERKANI KHELAF</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -6851,13 +6851,13 @@
         </is>
       </c>
       <c r="E59" s="8" t="n">
-        <v>99766.25</v>
+        <v>0</v>
       </c>
       <c r="F59" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G59" s="8" t="n">
-        <v>0</v>
+        <v>160000.06</v>
       </c>
       <c r="H59" s="8">
         <f>E59+F59-G59</f>
@@ -6867,12 +6867,12 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>C186</t>
+          <t>C164</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>DJOUDI SMAIL</t>
+          <t>ETS DJENNADI REYAD</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="E60" s="8" t="n">
-        <v>0</v>
+        <v>-4500000</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>232479</v>
+        <v>2441390.87</v>
       </c>
       <c r="G60" s="8" t="n">
         <v>0</v>
@@ -6902,12 +6902,12 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>C248</t>
+          <t>C174</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>SNC ECOTP MOUHALI ET FRERE</t>
+          <t>HAMMAOUI LAHDI</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -6921,13 +6921,13 @@
         </is>
       </c>
       <c r="E61" s="8" t="n">
-        <v>0</v>
+        <v>99766.25</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>587860</v>
+        <v>0</v>
       </c>
       <c r="G61" s="8" t="n">
-        <v>123760</v>
+        <v>0</v>
       </c>
       <c r="H61" s="8">
         <f>E61+F61-G61</f>
@@ -6937,12 +6937,12 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>C258</t>
+          <t>C186</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>AMEUR KHELLAF</t>
+          <t>DJOUDI SMAIL</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="E62" s="8" t="n">
-        <v>99837.81</v>
+        <v>0</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>0</v>
+        <v>232479</v>
       </c>
       <c r="G62" s="8" t="n">
         <v>0</v>
@@ -6972,12 +6972,12 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>C266</t>
+          <t>C248</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>BENSACI MESSAOUD</t>
+          <t>SNC ECOTP MOUHALI ET FRERE</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -6994,10 +6994,10 @@
         <v>0</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>0</v>
+        <v>587860</v>
       </c>
       <c r="G63" s="8" t="n">
-        <v>1063860</v>
+        <v>123760</v>
       </c>
       <c r="H63" s="8">
         <f>E63+F63-G63</f>
@@ -7007,12 +7007,12 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>C278</t>
+          <t>C258</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>BENAMARA AYOUB SAHARA MOTORS</t>
+          <t>AMEUR KHELLAF</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
@@ -7026,10 +7026,10 @@
         </is>
       </c>
       <c r="E64" s="8" t="n">
-        <v>-1989648</v>
+        <v>99837.81</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>980111.95</v>
+        <v>0</v>
       </c>
       <c r="G64" s="8" t="n">
         <v>0</v>
@@ -7042,12 +7042,12 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>C296</t>
+          <t>C266</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>SARL LOCA PREST</t>
+          <t>BENSACI MESSAOUD</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
@@ -7061,13 +7061,13 @@
         </is>
       </c>
       <c r="E65" s="8" t="n">
-        <v>707123.6800000001</v>
+        <v>0</v>
       </c>
       <c r="F65" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G65" s="8" t="n">
-        <v>0</v>
+        <v>1063860</v>
       </c>
       <c r="H65" s="8">
         <f>E65+F65-G65</f>
@@ -7077,12 +7077,12 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>C327</t>
+          <t>C278</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>HAMOUMOU ABDELLAH</t>
+          <t>BENAMARA AYOUB SAHARA MOTORS</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="E66" s="8" t="n">
-        <v>600000.01</v>
+        <v>-1989648</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>0</v>
+        <v>980111.95</v>
       </c>
       <c r="G66" s="8" t="n">
         <v>0</v>
@@ -7112,12 +7112,12 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>C359</t>
+          <t>C296</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>SELLAH LYES</t>
+          <t>SARL LOCA PREST</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
@@ -7131,10 +7131,10 @@
         </is>
       </c>
       <c r="E67" s="8" t="n">
-        <v>0</v>
+        <v>707123.6800000001</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>377860</v>
+        <v>0</v>
       </c>
       <c r="G67" s="8" t="n">
         <v>0</v>
@@ -7147,12 +7147,12 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>C441</t>
+          <t>C327</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>TICHAT HALIM</t>
+          <t>HAMOUMOU ABDELLAH</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
@@ -7166,10 +7166,10 @@
         </is>
       </c>
       <c r="E68" s="8" t="n">
-        <v>0</v>
+        <v>600000.01</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>1150000.1</v>
+        <v>0</v>
       </c>
       <c r="G68" s="8" t="n">
         <v>0</v>
@@ -7182,12 +7182,12 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>C444</t>
+          <t>C359</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>BOUROKBA MANSOUR</t>
+          <t>SELLAH LYES</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -7201,10 +7201,10 @@
         </is>
       </c>
       <c r="E69" s="8" t="n">
-        <v>300000.01</v>
+        <v>0</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>0</v>
+        <v>377860</v>
       </c>
       <c r="G69" s="8" t="n">
         <v>0</v>
@@ -7217,12 +7217,12 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>C494</t>
+          <t>C441</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>DOGGA TAHA</t>
+          <t>TICHAT HALIM</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
@@ -7239,7 +7239,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>300000</v>
+        <v>1150000.1</v>
       </c>
       <c r="G70" s="8" t="n">
         <v>0</v>
@@ -7252,12 +7252,12 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>C505</t>
+          <t>C444</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>EURL TRANSPORT FLY</t>
+          <t>BOUROKBA MANSOUR</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -7271,10 +7271,10 @@
         </is>
       </c>
       <c r="E71" s="8" t="n">
-        <v>0</v>
+        <v>300000.01</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>1190975</v>
+        <v>0</v>
       </c>
       <c r="G71" s="8" t="n">
         <v>0</v>
@@ -7287,12 +7287,12 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>C549</t>
+          <t>C494</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>SELLAH FARID</t>
+          <t>DOGGA TAHA</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
@@ -7309,7 +7309,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>55458</v>
+        <v>300000</v>
       </c>
       <c r="G72" s="8" t="n">
         <v>0</v>
@@ -7322,12 +7322,12 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>C556</t>
+          <t>C505</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>LAOUEDJ MOHAMMED SALEH</t>
+          <t>EURL TRANSPORT FLY</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -7344,10 +7344,10 @@
         <v>0</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>7069243.81</v>
+        <v>1190975</v>
       </c>
       <c r="G73" s="8" t="n">
-        <v>4914565.27</v>
+        <v>0</v>
       </c>
       <c r="H73" s="8">
         <f>E73+F73-G73</f>
@@ -7357,12 +7357,12 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>C594</t>
+          <t>C549</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>SARL DPR AXXAM BRIQUETERIE</t>
+          <t>SELLAH FARID</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="E74" s="8" t="n">
-        <v>371014451.28</v>
+        <v>0</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>0</v>
+        <v>55458</v>
       </c>
       <c r="G74" s="8" t="n">
         <v>0</v>
@@ -7392,12 +7392,12 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>C596</t>
+          <t>C556</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>COSIDER OUVRAGES D'ART SPA</t>
+          <t>LAOUEDJ MOHAMMED SALEH</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -7414,10 +7414,10 @@
         <v>0</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>304640</v>
+        <v>7069243.81</v>
       </c>
       <c r="G75" s="8" t="n">
-        <v>0</v>
+        <v>4914565.27</v>
       </c>
       <c r="H75" s="8">
         <f>E75+F75-G75</f>
@@ -7427,12 +7427,12 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>C599</t>
+          <t>C594</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>MOHELLEBI MOHAMED</t>
+          <t>SARL DPR AXXAM BRIQUETERIE</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="E76" s="8" t="n">
-        <v>0</v>
+        <v>371014451.28</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>898334.84</v>
+        <v>0</v>
       </c>
       <c r="G76" s="8" t="n">
         <v>0</v>
@@ -7462,12 +7462,12 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>C612</t>
+          <t>C596</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>ZIANI AMIR</t>
+          <t>COSIDER OUVRAGES D'ART SPA</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -7484,10 +7484,10 @@
         <v>0</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>1500000</v>
+        <v>304640</v>
       </c>
       <c r="G77" s="8" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="H77" s="8">
         <f>E77+F77-G77</f>
@@ -7497,12 +7497,12 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>C616</t>
+          <t>C599</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>NUMILOG SPA TRANSPORT ET LOGIS</t>
+          <t>MOHELLEBI MOHAMED</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
@@ -7516,13 +7516,13 @@
         </is>
       </c>
       <c r="E78" s="8" t="n">
-        <v>1586984</v>
+        <v>0</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>333200</v>
+        <v>898334.84</v>
       </c>
       <c r="G78" s="8" t="n">
-        <v>172550</v>
+        <v>0</v>
       </c>
       <c r="H78" s="8">
         <f>E78+F78-G78</f>
@@ -7532,12 +7532,12 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>C622</t>
+          <t>C612</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>MASSIOUN HAMZA</t>
+          <t>ZIANI AMIR</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -7554,10 +7554,10 @@
         <v>0</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>63000</v>
+        <v>1500000</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>0</v>
+        <v>3500000</v>
       </c>
       <c r="H79" s="8">
         <f>E79+F79-G79</f>
@@ -7567,12 +7567,12 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>C625</t>
+          <t>C616</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>AMIMER ENERGIE SPA</t>
+          <t>NUMILOG SPA TRANSPORT ET LOGIS</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
@@ -7586,13 +7586,13 @@
         </is>
       </c>
       <c r="E80" s="8" t="n">
-        <v>228480</v>
+        <v>1586984</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>0</v>
+        <v>333200</v>
       </c>
       <c r="G80" s="8" t="n">
-        <v>0</v>
+        <v>172550</v>
       </c>
       <c r="H80" s="8">
         <f>E80+F80-G80</f>
@@ -7602,12 +7602,12 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>C631</t>
+          <t>C622</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>BENAMMAR SOFIANE</t>
+          <t>MASSIOUN HAMZA</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -7624,7 +7624,7 @@
         <v>0</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>998257.67</v>
+        <v>63000</v>
       </c>
       <c r="G81" s="8" t="n">
         <v>0</v>
@@ -7637,12 +7637,12 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>C659</t>
+          <t>C625</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>HENIA MOHAMED ELBARK</t>
+          <t>AMIMER ENERGIE SPA</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
@@ -7656,7 +7656,7 @@
         </is>
       </c>
       <c r="E82" s="8" t="n">
-        <v>226000.01</v>
+        <v>228480</v>
       </c>
       <c r="F82" s="8" t="n">
         <v>0</v>
@@ -7672,12 +7672,12 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>C667</t>
+          <t>C631</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>SPA EVEMAC</t>
+          <t>BENAMMAR SOFIANE</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="E83" s="8" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>0</v>
+        <v>998257.67</v>
       </c>
       <c r="G83" s="8" t="n">
         <v>0</v>
@@ -7707,12 +7707,12 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>C668</t>
+          <t>C659</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>SARL SERVICES POIDS LOURDS</t>
+          <t>HENIA MOHAMED ELBARK</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
@@ -7726,13 +7726,13 @@
         </is>
       </c>
       <c r="E84" s="8" t="n">
-        <v>0</v>
+        <v>226000.01</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>5351550.01</v>
+        <v>0</v>
       </c>
       <c r="G84" s="8" t="n">
-        <v>5351550</v>
+        <v>0</v>
       </c>
       <c r="H84" s="8">
         <f>E84+F84-G84</f>
@@ -7742,12 +7742,12 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>C671</t>
+          <t>C667</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>SPA TMF LOGISTICS</t>
+          <t>SPA EVEMAC</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="E85" s="8" t="n">
-        <v>9248680</v>
+        <v>100000</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>9054234</v>
+        <v>0</v>
       </c>
       <c r="G85" s="8" t="n">
         <v>0</v>
@@ -7777,12 +7777,12 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>C676</t>
+          <t>C668</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>MADI AHMED</t>
+          <t>SARL SERVICES POIDS LOURDS</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
@@ -7799,10 +7799,10 @@
         <v>0</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>141181.56</v>
+        <v>5351550.01</v>
       </c>
       <c r="G86" s="8" t="n">
-        <v>141181.56</v>
+        <v>5351550</v>
       </c>
       <c r="H86" s="8">
         <f>E86+F86-G86</f>
@@ -7812,12 +7812,12 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>C692</t>
+          <t>C671</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>EURL CONPICAM</t>
+          <t>SPA TMF LOGISTICS</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="E87" s="8" t="n">
-        <v>584700.02</v>
+        <v>9248680</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>0</v>
+        <v>9054234</v>
       </c>
       <c r="G87" s="8" t="n">
         <v>0</v>
@@ -7847,12 +7847,12 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>C701</t>
+          <t>C676</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>BELKAID SAMIR</t>
+          <t>MADI AHMED</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
@@ -7866,13 +7866,13 @@
         </is>
       </c>
       <c r="E88" s="8" t="n">
-        <v>116300</v>
+        <v>0</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>0</v>
+        <v>141181.56</v>
       </c>
       <c r="G88" s="8" t="n">
-        <v>0</v>
+        <v>141181.56</v>
       </c>
       <c r="H88" s="8">
         <f>E88+F88-G88</f>
@@ -7882,12 +7882,12 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>C708</t>
+          <t>C692</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>BEJAIA LOGISTIQUE</t>
+          <t>EURL CONPICAM</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -7901,13 +7901,13 @@
         </is>
       </c>
       <c r="E89" s="8" t="n">
-        <v>7842460</v>
+        <v>584700.02</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>17063648</v>
+        <v>0</v>
       </c>
       <c r="G89" s="8" t="n">
-        <v>9241421</v>
+        <v>0</v>
       </c>
       <c r="H89" s="8">
         <f>E89+F89-G89</f>
@@ -7917,12 +7917,12 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>C710</t>
+          <t>C701</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>SPA TRANS OUEST</t>
+          <t>BELKAID SAMIR</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
@@ -7936,7 +7936,7 @@
         </is>
       </c>
       <c r="E90" s="8" t="n">
-        <v>76160</v>
+        <v>116300</v>
       </c>
       <c r="F90" s="8" t="n">
         <v>0</v>
@@ -7952,12 +7952,12 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>C721</t>
+          <t>C708</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>ENSP SPA</t>
+          <t>BEJAIA LOGISTIQUE</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
@@ -7971,13 +7971,13 @@
         </is>
       </c>
       <c r="E91" s="8" t="n">
-        <v>489329.16</v>
+        <v>7842460</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>0</v>
+        <v>17063648</v>
       </c>
       <c r="G91" s="8" t="n">
-        <v>0</v>
+        <v>10118570</v>
       </c>
       <c r="H91" s="8">
         <f>E91+F91-G91</f>
@@ -7987,12 +7987,12 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>C732</t>
+          <t>C710</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>NECHAB HACENE</t>
+          <t>SPA TRANS OUEST</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="E92" s="8" t="n">
-        <v>220150</v>
+        <v>76160</v>
       </c>
       <c r="F92" s="8" t="n">
         <v>0</v>
@@ -8022,12 +8022,12 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>C740</t>
+          <t>C721</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>EURL BS COMMERCE</t>
+          <t>ENSP SPA</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
@@ -8041,13 +8041,13 @@
         </is>
       </c>
       <c r="E93" s="8" t="n">
-        <v>0</v>
+        <v>489329.16</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>5743759.5</v>
+        <v>0</v>
       </c>
       <c r="G93" s="8" t="n">
-        <v>5743700</v>
+        <v>0</v>
       </c>
       <c r="H93" s="8">
         <f>E93+F93-G93</f>
@@ -8057,12 +8057,12 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>C752</t>
+          <t>C732</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>SPA METIDJI TRANS DE MARCHANDI</t>
+          <t>NECHAB HACENE</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="E94" s="8" t="n">
-        <v>29750</v>
+        <v>220150</v>
       </c>
       <c r="F94" s="8" t="n">
         <v>0</v>
@@ -8092,12 +8092,12 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>C759</t>
+          <t>C740</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>HANIFI SALAH</t>
+          <t>EURL BS COMMERCE</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="F95" s="8" t="n">
-        <v>139740</v>
+        <v>5743759.5</v>
       </c>
       <c r="G95" s="8" t="n">
-        <v>112370</v>
+        <v>5743700</v>
       </c>
       <c r="H95" s="8">
         <f>E95+F95-G95</f>
@@ -8127,12 +8127,12 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>C784</t>
+          <t>C752</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>EURL MONTE PARTS</t>
+          <t>SPA METIDJI TRANS DE MARCHANDI</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
@@ -8146,7 +8146,7 @@
         </is>
       </c>
       <c r="E96" s="8" t="n">
-        <v>74000</v>
+        <v>29750</v>
       </c>
       <c r="F96" s="8" t="n">
         <v>0</v>
@@ -8162,12 +8162,12 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>C816</t>
+          <t>C759</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>EPE SPA FERROVIAL</t>
+          <t>HANIFI SALAH</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -8181,13 +8181,13 @@
         </is>
       </c>
       <c r="E97" s="8" t="n">
-        <v>1187620</v>
+        <v>0</v>
       </c>
       <c r="F97" s="8" t="n">
-        <v>714000</v>
+        <v>139740</v>
       </c>
       <c r="G97" s="8" t="n">
-        <v>0</v>
+        <v>112370</v>
       </c>
       <c r="H97" s="8">
         <f>E97+F97-G97</f>
@@ -8197,12 +8197,12 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>C819</t>
+          <t>C784</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>SNC MOTEUR BLUE ZIANI ET CIE</t>
+          <t>EURL MONTE PARTS</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
@@ -8216,7 +8216,7 @@
         </is>
       </c>
       <c r="E98" s="8" t="n">
-        <v>1000000</v>
+        <v>74000</v>
       </c>
       <c r="F98" s="8" t="n">
         <v>0</v>
@@ -8232,12 +8232,12 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>C831</t>
+          <t>C816</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>DERDOURI FAROUK</t>
+          <t>EPE SPA FERROVIAL</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -8251,10 +8251,10 @@
         </is>
       </c>
       <c r="E99" s="8" t="n">
-        <v>0</v>
+        <v>1187620</v>
       </c>
       <c r="F99" s="8" t="n">
-        <v>2681300.09</v>
+        <v>714000</v>
       </c>
       <c r="G99" s="8" t="n">
         <v>0</v>
@@ -8267,12 +8267,12 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>C863</t>
+          <t>C819</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>SARL GRANIT NEGOCE TRANSPORT</t>
+          <t>SNC MOTEUR BLUE ZIANI ET CIE</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
@@ -8286,7 +8286,7 @@
         </is>
       </c>
       <c r="E100" s="8" t="n">
-        <v>-32844</v>
+        <v>1000000</v>
       </c>
       <c r="F100" s="8" t="n">
         <v>0</v>
@@ -8302,12 +8302,12 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>C876</t>
+          <t>C831</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>GHENABZIA BELKACEM</t>
+          <t>DERDOURI FAROUK</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
@@ -8321,10 +8321,10 @@
         </is>
       </c>
       <c r="E101" s="8" t="n">
-        <v>185540</v>
+        <v>0</v>
       </c>
       <c r="F101" s="8" t="n">
-        <v>0</v>
+        <v>2681300.09</v>
       </c>
       <c r="G101" s="8" t="n">
         <v>0</v>
@@ -8337,12 +8337,12 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>C887</t>
+          <t>C863</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>SARL COMPLEXE AGRO ALIMENTAIRE</t>
+          <t>SARL GRANIT NEGOCE TRANSPORT</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
@@ -8356,7 +8356,7 @@
         </is>
       </c>
       <c r="E102" s="8" t="n">
-        <v>60690</v>
+        <v>-32844</v>
       </c>
       <c r="F102" s="8" t="n">
         <v>0</v>
@@ -8372,12 +8372,12 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>C891</t>
+          <t>C876</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>SACI MOUSSA</t>
+          <t>GHENABZIA BELKACEM</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
@@ -8391,10 +8391,10 @@
         </is>
       </c>
       <c r="E103" s="8" t="n">
-        <v>0</v>
+        <v>185540</v>
       </c>
       <c r="F103" s="8" t="n">
-        <v>192499.99</v>
+        <v>0</v>
       </c>
       <c r="G103" s="8" t="n">
         <v>0</v>
@@ -8407,12 +8407,12 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>C900</t>
+          <t>C887</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>BENAMARA MOHAMMED</t>
+          <t>SARL COMPLEXE AGRO ALIMENTAIRE</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
@@ -8426,10 +8426,10 @@
         </is>
       </c>
       <c r="E104" s="8" t="n">
-        <v>1989648</v>
+        <v>60690</v>
       </c>
       <c r="F104" s="8" t="n">
-        <v>995067.48</v>
+        <v>0</v>
       </c>
       <c r="G104" s="8" t="n">
         <v>0</v>
@@ -8442,12 +8442,12 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>C907</t>
+          <t>C891</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>SARL EURODAX TRUCKS</t>
+          <t>SACI MOUSSA</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
@@ -8464,7 +8464,7 @@
         <v>0</v>
       </c>
       <c r="F105" s="8" t="n">
-        <v>760600.02</v>
+        <v>192499.99</v>
       </c>
       <c r="G105" s="8" t="n">
         <v>0</v>
@@ -8477,12 +8477,12 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>C910</t>
+          <t>C900</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>SASSANE RAMDANE</t>
+          <t>BENAMARA MOHAMMED</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -8496,10 +8496,10 @@
         </is>
       </c>
       <c r="E106" s="8" t="n">
-        <v>0</v>
+        <v>1989648</v>
       </c>
       <c r="F106" s="8" t="n">
-        <v>391358.01</v>
+        <v>995067.48</v>
       </c>
       <c r="G106" s="8" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>C916</t>
+          <t>C907</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>ZIANI LAKHDAR</t>
+          <t>SARL EURODAX TRUCKS</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
@@ -8534,10 +8534,10 @@
         <v>0</v>
       </c>
       <c r="F107" s="8" t="n">
-        <v>4202000</v>
+        <v>760600.02</v>
       </c>
       <c r="G107" s="8" t="n">
-        <v>1472000</v>
+        <v>0</v>
       </c>
       <c r="H107" s="8">
         <f>E107+F107-G107</f>
@@ -8547,12 +8547,12 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>C918</t>
+          <t>C910</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>TILKOUT AHCENE</t>
+          <t>SASSANE RAMDANE</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -8569,7 +8569,7 @@
         <v>0</v>
       </c>
       <c r="F108" s="8" t="n">
-        <v>732500</v>
+        <v>391358.01</v>
       </c>
       <c r="G108" s="8" t="n">
         <v>0</v>
@@ -8582,12 +8582,12 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>C925</t>
+          <t>C916</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>SPA AGEFAL</t>
+          <t>ZIANI LAKHDAR</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
@@ -8601,13 +8601,13 @@
         </is>
       </c>
       <c r="E109" s="8" t="n">
-        <v>60214</v>
+        <v>0</v>
       </c>
       <c r="F109" s="8" t="n">
-        <v>0</v>
+        <v>4202000</v>
       </c>
       <c r="G109" s="8" t="n">
-        <v>0</v>
+        <v>1472000</v>
       </c>
       <c r="H109" s="8">
         <f>E109+F109-G109</f>
@@ -8617,12 +8617,12 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>C928</t>
+          <t>C918</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>SARL YAYA LOUNIS ET FRERES TRA</t>
+          <t>TILKOUT AHCENE</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
@@ -8639,7 +8639,7 @@
         <v>0</v>
       </c>
       <c r="F110" s="8" t="n">
-        <v>170000</v>
+        <v>732500</v>
       </c>
       <c r="G110" s="8" t="n">
         <v>0</v>
@@ -8652,12 +8652,12 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>C934</t>
+          <t>C925</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>SARL ROYAL MATERIAUX DE CONST</t>
+          <t>SPA AGEFAL</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="E111" s="8" t="n">
-        <v>0</v>
+        <v>60214</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>1139300.02</v>
+        <v>0</v>
       </c>
       <c r="G111" s="8" t="n">
         <v>0</v>
@@ -8687,12 +8687,12 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>C959</t>
+          <t>C928</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>EURL TERRENO TRANS</t>
+          <t>SARL YAYA LOUNIS ET FRERES TRA</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="E112" s="8" t="n">
-        <v>1420860</v>
+        <v>0</v>
       </c>
       <c r="F112" s="8" t="n">
-        <v>12165489</v>
+        <v>170000</v>
       </c>
       <c r="G112" s="8" t="n">
         <v>0</v>
@@ -8722,12 +8722,12 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>C968</t>
+          <t>C934</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>SARL MTA</t>
+          <t>SARL ROYAL MATERIAUX DE CONST</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="E113" s="8" t="n">
-        <v>151844</v>
+        <v>0</v>
       </c>
       <c r="F113" s="8" t="n">
-        <v>0</v>
+        <v>1139300.02</v>
       </c>
       <c r="G113" s="8" t="n">
         <v>0</v>
@@ -8757,12 +8757,12 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>C973</t>
+          <t>C959</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>ZIANI BILAL</t>
+          <t>EURL TERRENO TRANS</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
@@ -8776,10 +8776,10 @@
         </is>
       </c>
       <c r="E114" s="8" t="n">
-        <v>0</v>
+        <v>1420860</v>
       </c>
       <c r="F114" s="8" t="n">
-        <v>2000390</v>
+        <v>12165489</v>
       </c>
       <c r="G114" s="8" t="n">
         <v>0</v>
@@ -8792,12 +8792,12 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>C975</t>
+          <t>C968</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>SAHRAOUI BECHAGHA</t>
+          <t>SARL MTA</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
@@ -8811,10 +8811,10 @@
         </is>
       </c>
       <c r="E115" s="8" t="n">
-        <v>0</v>
+        <v>151844</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>1241000.01</v>
+        <v>0</v>
       </c>
       <c r="G115" s="8" t="n">
         <v>0</v>
@@ -8827,12 +8827,12 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>C978</t>
+          <t>C973</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>SPA AGGLOMERES DE L'EST</t>
+          <t>ZIANI BILAL</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
@@ -8846,10 +8846,10 @@
         </is>
       </c>
       <c r="E116" s="8" t="n">
-        <v>67830</v>
+        <v>0</v>
       </c>
       <c r="F116" s="8" t="n">
-        <v>318920</v>
+        <v>2000390</v>
       </c>
       <c r="G116" s="8" t="n">
         <v>0</v>
@@ -8862,12 +8862,12 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>C980</t>
+          <t>C975</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>BOUHAMED ABDERRAHIM</t>
+          <t>SAHRAOUI BECHAGHA</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
@@ -8884,10 +8884,10 @@
         <v>0</v>
       </c>
       <c r="F117" s="8" t="n">
-        <v>857289</v>
+        <v>1241000.01</v>
       </c>
       <c r="G117" s="8" t="n">
-        <v>0</v>
+        <v>887700</v>
       </c>
       <c r="H117" s="8">
         <f>E117+F117-G117</f>
@@ -8897,12 +8897,12 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>C986</t>
+          <t>C978</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>SARL LAITERIE SOUMMAM</t>
+          <t>SPA AGGLOMERES DE L'EST</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
@@ -8916,10 +8916,10 @@
         </is>
       </c>
       <c r="E118" s="8" t="n">
-        <v>0</v>
+        <v>67830</v>
       </c>
       <c r="F118" s="8" t="n">
-        <v>3141600</v>
+        <v>318920</v>
       </c>
       <c r="G118" s="8" t="n">
         <v>0</v>
@@ -8932,29 +8932,29 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>AC002</t>
+          <t>C980</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>DJENNADI AHCENE</t>
+          <t>BOUHAMED ABDERRAHIM</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>41900</t>
+          <t>41100</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Clients créditeurs -avances re</t>
+          <t>Clients</t>
         </is>
       </c>
       <c r="E119" s="8" t="n">
-        <v>-500000</v>
+        <v>0</v>
       </c>
       <c r="F119" s="8" t="n">
-        <v>0</v>
+        <v>857289</v>
       </c>
       <c r="G119" s="8" t="n">
         <v>0</v>
@@ -8967,29 +8967,29 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>AC009</t>
+          <t>C986</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>SARL DPR AXXAM</t>
+          <t>SARL LAITERIE SOUMMAM</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>41900</t>
+          <t>41100</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>Clients créditeurs -avances re</t>
+          <t>Clients</t>
         </is>
       </c>
       <c r="E120" s="8" t="n">
-        <v>-9821942.210000001</v>
+        <v>0</v>
       </c>
       <c r="F120" s="8" t="n">
-        <v>0</v>
+        <v>3141600</v>
       </c>
       <c r="G120" s="8" t="n">
         <v>0</v>
@@ -9002,12 +9002,12 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>AC014</t>
+          <t>AC002</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>SARL TRANS FAID</t>
+          <t>DJENNADI AHCENE</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="E121" s="8" t="n">
-        <v>-1843316.12</v>
+        <v>-500000</v>
       </c>
       <c r="F121" s="8" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>AC048</t>
+          <t>AC009</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>MADI ALLAOUA</t>
+          <t>SARL DPR AXXAM</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="E122" s="8" t="n">
-        <v>-2660000</v>
+        <v>-9821942.210000001</v>
       </c>
       <c r="F122" s="8" t="n">
         <v>0</v>
@@ -9072,12 +9072,12 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>AC067</t>
+          <t>AC014</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>DJENNADI REYAD</t>
+          <t>SARL TRANS FAID</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
@@ -9091,7 +9091,7 @@
         </is>
       </c>
       <c r="E123" s="8" t="n">
-        <v>-17609544.19</v>
+        <v>-1843316.12</v>
       </c>
       <c r="F123" s="8" t="n">
         <v>0</v>
@@ -9107,12 +9107,12 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>AC111</t>
+          <t>AC048</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>SNC NASAF GALOUL ET CIE</t>
+          <t>MADI ALLAOUA</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
@@ -9126,7 +9126,7 @@
         </is>
       </c>
       <c r="E124" s="8" t="n">
-        <v>-1929169.53</v>
+        <v>-2660000</v>
       </c>
       <c r="F124" s="8" t="n">
         <v>0</v>
@@ -9142,12 +9142,12 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>AC129</t>
+          <t>AC067</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>HAGROUD ABD ELAZIZE</t>
+          <t>DJENNADI REYAD</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="E125" s="8" t="n">
-        <v>-48000</v>
+        <v>-17609544.19</v>
       </c>
       <c r="F125" s="8" t="n">
         <v>0</v>
@@ -9177,12 +9177,12 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>AC144</t>
+          <t>AC111</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>SELLAH ABD ELGHANI</t>
+          <t>SNC NASAF GALOUL ET CIE</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="E126" s="8" t="n">
-        <v>-300000</v>
+        <v>-1929169.53</v>
       </c>
       <c r="F126" s="8" t="n">
         <v>0</v>
@@ -9212,12 +9212,12 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>AC145</t>
+          <t>AC129</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>EURL CARRIER LES BIBIANS</t>
+          <t>HAGROUD ABD ELAZIZE</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="E127" s="8" t="n">
-        <v>-800000</v>
+        <v>-48000</v>
       </c>
       <c r="F127" s="8" t="n">
         <v>0</v>
@@ -9247,12 +9247,12 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>AC189</t>
+          <t>AC144</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>MECHREF MOUHOUB</t>
+          <t>SELLAH ABD ELGHANI</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="E128" s="8" t="n">
-        <v>-3509008.27</v>
+        <v>-300000</v>
       </c>
       <c r="F128" s="8" t="n">
         <v>0</v>
@@ -9282,12 +9282,12 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>AC191</t>
+          <t>AC145</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>OUKHALED YASSINE</t>
+          <t>EURL CARRIER LES BIBIANS</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="E129" s="8" t="n">
-        <v>-5638.26</v>
+        <v>-800000</v>
       </c>
       <c r="F129" s="8" t="n">
         <v>0</v>
@@ -9317,12 +9317,12 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>AC206</t>
+          <t>AC189</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>CHEBBAH NACER</t>
+          <t>MECHREF MOUHOUB</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="E130" s="8" t="n">
-        <v>-100000</v>
+        <v>-3509008.27</v>
       </c>
       <c r="F130" s="8" t="n">
         <v>0</v>
@@ -9352,12 +9352,12 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>AC207</t>
+          <t>AC191</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>BOUKIR KHELLAF</t>
+          <t>OUKHALED YASSINE</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="E131" s="8" t="n">
-        <v>-565666.61</v>
+        <v>-5638.26</v>
       </c>
       <c r="F131" s="8" t="n">
         <v>0</v>
@@ -9387,12 +9387,12 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>AC211</t>
+          <t>AC206</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>MENACERI LARBI</t>
+          <t>CHEBBAH NACER</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="E132" s="8" t="n">
-        <v>-280029.09</v>
+        <v>-100000</v>
       </c>
       <c r="F132" s="8" t="n">
         <v>0</v>
@@ -9422,12 +9422,12 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>AC212</t>
+          <t>AC207</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>ACHOURI ABDELLATIF</t>
+          <t>BOUKIR KHELLAF</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
@@ -9441,7 +9441,7 @@
         </is>
       </c>
       <c r="E133" s="8" t="n">
-        <v>-1500000</v>
+        <v>-565666.61</v>
       </c>
       <c r="F133" s="8" t="n">
         <v>0</v>
@@ -9457,12 +9457,12 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>AC213</t>
+          <t>AC211</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>NABET NADIR</t>
+          <t>MENACERI LARBI</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="E134" s="8" t="n">
-        <v>-661017.3199999999</v>
+        <v>-280029.09</v>
       </c>
       <c r="F134" s="8" t="n">
         <v>0</v>
@@ -9492,12 +9492,12 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>AC220</t>
+          <t>AC212</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>AOUCHICHE MASSINISSA</t>
+          <t>ACHOURI ABDELLATIF</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
@@ -9511,7 +9511,7 @@
         </is>
       </c>
       <c r="E135" s="8" t="n">
-        <v>-210129</v>
+        <v>-1500000</v>
       </c>
       <c r="F135" s="8" t="n">
         <v>0</v>
@@ -9527,12 +9527,12 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>AC222</t>
+          <t>AC213</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>MAHAH ACHOUR</t>
+          <t>NABET NADIR</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
@@ -9546,7 +9546,7 @@
         </is>
       </c>
       <c r="E136" s="8" t="n">
-        <v>-656638.71</v>
+        <v>-661017.3199999999</v>
       </c>
       <c r="F136" s="8" t="n">
         <v>0</v>
@@ -9562,12 +9562,12 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>AC223</t>
+          <t>AC220</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>AYACHE ABDELFATEH</t>
+          <t>AOUCHICHE MASSINISSA</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="E137" s="8" t="n">
-        <v>-1259817.91</v>
+        <v>-210129</v>
       </c>
       <c r="F137" s="8" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>AC224</t>
+          <t>AC222</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>BOUKAIBA SAMIR</t>
+          <t>MAHAH ACHOUR</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="E138" s="8" t="n">
-        <v>-999466.3199999999</v>
+        <v>-656638.71</v>
       </c>
       <c r="F138" s="8" t="n">
         <v>0</v>
@@ -9632,12 +9632,12 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>AC225</t>
+          <t>AC223</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>AZIB AZZEDINE</t>
+          <t>AYACHE ABDELFATEH</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
@@ -9651,7 +9651,7 @@
         </is>
       </c>
       <c r="E139" s="8" t="n">
-        <v>-4087093.07</v>
+        <v>-1259817.91</v>
       </c>
       <c r="F139" s="8" t="n">
         <v>0</v>
@@ -9667,12 +9667,12 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>AC229</t>
+          <t>AC224</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>SARL REV ETPBH SIDANE</t>
+          <t>BOUKAIBA SAMIR</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="E140" s="8" t="n">
-        <v>-393539.72</v>
+        <v>-999466.3199999999</v>
       </c>
       <c r="F140" s="8" t="n">
         <v>0</v>
@@ -9702,12 +9702,12 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>AC230</t>
+          <t>AC225</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>LAIDANI NABIL</t>
+          <t>AZIB AZZEDINE</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
@@ -9721,7 +9721,7 @@
         </is>
       </c>
       <c r="E141" s="8" t="n">
-        <v>-652291.4399999999</v>
+        <v>-4087093.07</v>
       </c>
       <c r="F141" s="8" t="n">
         <v>0</v>
@@ -9737,12 +9737,12 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>AC233</t>
+          <t>AC229</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>IKHLEF DJELLOUL</t>
+          <t>SARL REV ETPBH SIDANE</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
@@ -9756,7 +9756,7 @@
         </is>
       </c>
       <c r="E142" s="8" t="n">
-        <v>-298000</v>
+        <v>-393539.72</v>
       </c>
       <c r="F142" s="8" t="n">
         <v>0</v>
@@ -9772,12 +9772,12 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>AC234</t>
+          <t>AC230</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>ABDELLI ABDENOUR</t>
+          <t>LAIDANI NABIL</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="E143" s="8" t="n">
-        <v>-292000</v>
+        <v>-652291.4399999999</v>
       </c>
       <c r="F143" s="8" t="n">
         <v>0</v>
@@ -9807,12 +9807,12 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>AC238</t>
+          <t>AC233</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>NAIT LARBI BOUALEM</t>
+          <t>IKHLEF DJELLOUL</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="E144" s="8" t="n">
-        <v>-20000</v>
+        <v>-298000</v>
       </c>
       <c r="F144" s="8" t="n">
         <v>0</v>
@@ -9842,12 +9842,12 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>AC302</t>
+          <t>AC234</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>ETB TCE AZIRI FARID</t>
+          <t>ABDELLI ABDENOUR</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
@@ -9861,7 +9861,7 @@
         </is>
       </c>
       <c r="E145" s="8" t="n">
-        <v>-9627609.779999999</v>
+        <v>-292000</v>
       </c>
       <c r="F145" s="8" t="n">
         <v>0</v>
@@ -9877,12 +9877,12 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>AC303</t>
+          <t>AC238</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>DJOUADI BELKACEM</t>
+          <t>NAIT LARBI BOUALEM</t>
         </is>
       </c>
       <c r="C146" s="7" t="inlineStr">
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="E146" s="8" t="n">
-        <v>-14706831.93</v>
+        <v>-20000</v>
       </c>
       <c r="F146" s="8" t="n">
         <v>0</v>
@@ -9912,12 +9912,12 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>AC304</t>
+          <t>AC302</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>ZIANI KOCEILA</t>
+          <t>ETB TCE AZIRI FARID</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
@@ -9931,7 +9931,7 @@
         </is>
       </c>
       <c r="E147" s="8" t="n">
-        <v>-5974969.31</v>
+        <v>-9627609.779999999</v>
       </c>
       <c r="F147" s="8" t="n">
         <v>0</v>
@@ -9947,12 +9947,12 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>AC305</t>
+          <t>AC303</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>AIT MOUSSA HANAFI</t>
+          <t>DJOUADI BELKACEM</t>
         </is>
       </c>
       <c r="C148" s="7" t="inlineStr">
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="E148" s="8" t="n">
-        <v>-38000</v>
+        <v>-14706831.93</v>
       </c>
       <c r="F148" s="8" t="n">
         <v>0</v>
@@ -9982,12 +9982,12 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>AC308</t>
+          <t>AC304</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>SARL TRANS SABLE D'OR</t>
+          <t>ZIANI KOCEILA</t>
         </is>
       </c>
       <c r="C149" s="7" t="inlineStr">
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="E149" s="8" t="n">
-        <v>-29298614.61</v>
+        <v>-5974969.31</v>
       </c>
       <c r="F149" s="8" t="n">
         <v>0</v>
@@ -10017,12 +10017,12 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>AC310</t>
+          <t>AC305</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>KRID FATMA ZOHRA</t>
+          <t>AIT MOUSSA HANAFI</t>
         </is>
       </c>
       <c r="C150" s="7" t="inlineStr">
@@ -10036,7 +10036,7 @@
         </is>
       </c>
       <c r="E150" s="8" t="n">
-        <v>-550000</v>
+        <v>-38000</v>
       </c>
       <c r="F150" s="8" t="n">
         <v>0</v>
@@ -10052,12 +10052,12 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>AC312</t>
+          <t>AC308</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>SARL KECHAYACHE BAT ET ROUTES</t>
+          <t>SARL TRANS SABLE D'OR</t>
         </is>
       </c>
       <c r="C151" s="7" t="inlineStr">
@@ -10071,7 +10071,7 @@
         </is>
       </c>
       <c r="E151" s="8" t="n">
-        <v>-1835871.17</v>
+        <v>-29298614.61</v>
       </c>
       <c r="F151" s="8" t="n">
         <v>0</v>
@@ -10087,12 +10087,12 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>AC313</t>
+          <t>AC310</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>SARL AHRAS ELECTRO DIESEL</t>
+          <t>KRID FATMA ZOHRA</t>
         </is>
       </c>
       <c r="C152" s="7" t="inlineStr">
@@ -10106,7 +10106,7 @@
         </is>
       </c>
       <c r="E152" s="8" t="n">
-        <v>-599999.99</v>
+        <v>-550000</v>
       </c>
       <c r="F152" s="8" t="n">
         <v>0</v>
@@ -10122,12 +10122,12 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>AC314</t>
+          <t>AC312</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>GUENDOUZ FERHAT B/BOUZIDI</t>
+          <t>SARL KECHAYACHE BAT ET ROUTES</t>
         </is>
       </c>
       <c r="C153" s="7" t="inlineStr">
@@ -10141,7 +10141,7 @@
         </is>
       </c>
       <c r="E153" s="8" t="n">
-        <v>-1000000</v>
+        <v>-1835871.17</v>
       </c>
       <c r="F153" s="8" t="n">
         <v>0</v>
@@ -10157,12 +10157,12 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>AC316</t>
+          <t>AC313</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>SNC BOVA YASSA ET CIE</t>
+          <t>SARL AHRAS ELECTRO DIESEL</t>
         </is>
       </c>
       <c r="C154" s="7" t="inlineStr">
@@ -10176,7 +10176,7 @@
         </is>
       </c>
       <c r="E154" s="8" t="n">
-        <v>-802295.0699999999</v>
+        <v>-599999.99</v>
       </c>
       <c r="F154" s="8" t="n">
         <v>0</v>
@@ -10192,12 +10192,12 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>AC317</t>
+          <t>AC314</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>ZIANI AISSA</t>
+          <t>GUENDOUZ FERHAT B/BOUZIDI</t>
         </is>
       </c>
       <c r="C155" s="7" t="inlineStr">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="E155" s="8" t="n">
-        <v>-883362.91</v>
+        <v>-1000000</v>
       </c>
       <c r="F155" s="8" t="n">
         <v>0</v>
@@ -10227,12 +10227,12 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>AC318</t>
+          <t>AC316</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>LEBSIR NADIA</t>
+          <t>SNC BOVA YASSA ET CIE</t>
         </is>
       </c>
       <c r="C156" s="7" t="inlineStr">
@@ -10246,7 +10246,7 @@
         </is>
       </c>
       <c r="E156" s="8" t="n">
-        <v>-400028.85</v>
+        <v>-802295.0699999999</v>
       </c>
       <c r="F156" s="8" t="n">
         <v>0</v>
@@ -10262,12 +10262,12 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>AC319</t>
+          <t>AC317</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>RECHRECHE YOUCEF</t>
+          <t>ZIANI AISSA</t>
         </is>
       </c>
       <c r="C157" s="7" t="inlineStr">
@@ -10281,7 +10281,7 @@
         </is>
       </c>
       <c r="E157" s="8" t="n">
-        <v>-800016.86</v>
+        <v>-883362.91</v>
       </c>
       <c r="F157" s="8" t="n">
         <v>0</v>
@@ -10297,12 +10297,12 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>AC320</t>
+          <t>AC318</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>MENHANE FARIDA</t>
+          <t>LEBSIR NADIA</t>
         </is>
       </c>
       <c r="C158" s="7" t="inlineStr">
@@ -10316,7 +10316,7 @@
         </is>
       </c>
       <c r="E158" s="8" t="n">
-        <v>-800012.53</v>
+        <v>-400028.85</v>
       </c>
       <c r="F158" s="8" t="n">
         <v>0</v>
@@ -10332,12 +10332,12 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>AC322</t>
+          <t>AC319</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>TIGHIDET ABDELMADJID</t>
+          <t>RECHRECHE YOUCEF</t>
         </is>
       </c>
       <c r="C159" s="7" t="inlineStr">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="E159" s="8" t="n">
-        <v>-254124</v>
+        <v>-800016.86</v>
       </c>
       <c r="F159" s="8" t="n">
         <v>0</v>
@@ -10367,12 +10367,12 @@
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>AC323</t>
+          <t>AC320</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>SARL VMLI</t>
+          <t>MENHANE FARIDA</t>
         </is>
       </c>
       <c r="C160" s="7" t="inlineStr">
@@ -10386,7 +10386,7 @@
         </is>
       </c>
       <c r="E160" s="8" t="n">
-        <v>-551850</v>
+        <v>-800012.53</v>
       </c>
       <c r="F160" s="8" t="n">
         <v>0</v>
@@ -10402,12 +10402,12 @@
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>AC326</t>
+          <t>AC322</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>DJOUMI LAID</t>
+          <t>TIGHIDET ABDELMADJID</t>
         </is>
       </c>
       <c r="C161" s="7" t="inlineStr">
@@ -10421,7 +10421,7 @@
         </is>
       </c>
       <c r="E161" s="8" t="n">
-        <v>-1881191.91</v>
+        <v>-254124</v>
       </c>
       <c r="F161" s="8" t="n">
         <v>0</v>
@@ -10437,12 +10437,12 @@
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>AC329</t>
+          <t>AC323</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>BOUHZILA MOURAD</t>
+          <t>SARL VMLI</t>
         </is>
       </c>
       <c r="C162" s="7" t="inlineStr">
@@ -10456,7 +10456,7 @@
         </is>
       </c>
       <c r="E162" s="8" t="n">
-        <v>-6695583.64</v>
+        <v>-551850</v>
       </c>
       <c r="F162" s="8" t="n">
         <v>0</v>
@@ -10472,12 +10472,12 @@
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>AC330</t>
+          <t>AC326</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>HENNOUNI ALI</t>
+          <t>DJOUMI LAID</t>
         </is>
       </c>
       <c r="C163" s="7" t="inlineStr">
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="E163" s="8" t="n">
-        <v>-705000</v>
+        <v>-1881191.91</v>
       </c>
       <c r="F163" s="8" t="n">
         <v>0</v>
@@ -10507,12 +10507,12 @@
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>AC331</t>
+          <t>AC329</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>OUASDI SAADI</t>
+          <t>BOUHZILA MOURAD</t>
         </is>
       </c>
       <c r="C164" s="7" t="inlineStr">
@@ -10526,7 +10526,7 @@
         </is>
       </c>
       <c r="E164" s="8" t="n">
-        <v>-2583217.7</v>
+        <v>-6695583.64</v>
       </c>
       <c r="F164" s="8" t="n">
         <v>0</v>
@@ -10542,12 +10542,12 @@
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>AC332</t>
+          <t>AC330</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>DJOUDI SADEK</t>
+          <t>HENNOUNI ALI</t>
         </is>
       </c>
       <c r="C165" s="7" t="inlineStr">
@@ -10561,7 +10561,7 @@
         </is>
       </c>
       <c r="E165" s="8" t="n">
-        <v>-3643857.92</v>
+        <v>-705000</v>
       </c>
       <c r="F165" s="8" t="n">
         <v>0</v>
@@ -10577,12 +10577,12 @@
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>AC333</t>
+          <t>AC331</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>YAHIAOUI REDOUANE</t>
+          <t>OUASDI SAADI</t>
         </is>
       </c>
       <c r="C166" s="7" t="inlineStr">
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="E166" s="8" t="n">
-        <v>-1897517.28</v>
+        <v>-2583217.7</v>
       </c>
       <c r="F166" s="8" t="n">
         <v>0</v>
@@ -10612,12 +10612,12 @@
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>AC335</t>
+          <t>AC332</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>BOUDJIT TAHAR</t>
+          <t>DJOUDI SADEK</t>
         </is>
       </c>
       <c r="C167" s="7" t="inlineStr">
@@ -10631,7 +10631,7 @@
         </is>
       </c>
       <c r="E167" s="8" t="n">
-        <v>-817760.04</v>
+        <v>-3643857.92</v>
       </c>
       <c r="F167" s="8" t="n">
         <v>0</v>
@@ -10647,12 +10647,12 @@
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>AC336</t>
+          <t>AC333</t>
         </is>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>GHANEM BRAHIM</t>
+          <t>YAHIAOUI REDOUANE</t>
         </is>
       </c>
       <c r="C168" s="7" t="inlineStr">
@@ -10666,7 +10666,7 @@
         </is>
       </c>
       <c r="E168" s="8" t="n">
-        <v>-502131.67</v>
+        <v>-1897517.28</v>
       </c>
       <c r="F168" s="8" t="n">
         <v>0</v>
@@ -10682,12 +10682,12 @@
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>AC337</t>
+          <t>AC335</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>IGHEMOURACENE SALIM</t>
+          <t>BOUDJIT TAHAR</t>
         </is>
       </c>
       <c r="C169" s="7" t="inlineStr">
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="E169" s="8" t="n">
-        <v>-10191211.8</v>
+        <v>-817760.04</v>
       </c>
       <c r="F169" s="8" t="n">
         <v>0</v>
@@ -10717,12 +10717,12 @@
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>AC338</t>
+          <t>AC336</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>FERROUDJ NASSIM</t>
+          <t>GHANEM BRAHIM</t>
         </is>
       </c>
       <c r="C170" s="7" t="inlineStr">
@@ -10736,7 +10736,7 @@
         </is>
       </c>
       <c r="E170" s="8" t="n">
-        <v>-497156.75</v>
+        <v>-502131.67</v>
       </c>
       <c r="F170" s="8" t="n">
         <v>0</v>
@@ -10752,12 +10752,12 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>AC339</t>
+          <t>AC337</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>BERKANI HAMZA</t>
+          <t>IGHEMOURACENE SALIM</t>
         </is>
       </c>
       <c r="C171" s="7" t="inlineStr">
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="E171" s="8" t="n">
-        <v>-2662204.95</v>
+        <v>-10191211.8</v>
       </c>
       <c r="F171" s="8" t="n">
         <v>0</v>
@@ -10787,12 +10787,12 @@
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>AC340</t>
+          <t>AC338</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>ZAIDANI ALI</t>
+          <t>FERROUDJ NASSIM</t>
         </is>
       </c>
       <c r="C172" s="7" t="inlineStr">
@@ -10806,7 +10806,7 @@
         </is>
       </c>
       <c r="E172" s="8" t="n">
-        <v>-12329618.11</v>
+        <v>-497156.75</v>
       </c>
       <c r="F172" s="8" t="n">
         <v>0</v>
@@ -10822,12 +10822,12 @@
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>AC341</t>
+          <t>AC339</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>HADDAD KHELLAF</t>
+          <t>BERKANI HAMZA</t>
         </is>
       </c>
       <c r="C173" s="7" t="inlineStr">
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="E173" s="8" t="n">
-        <v>-2072726.88</v>
+        <v>-2662204.95</v>
       </c>
       <c r="F173" s="8" t="n">
         <v>0</v>
@@ -10857,12 +10857,12 @@
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>AC343</t>
+          <t>AC340</t>
         </is>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>YAKOUBI MEZIANE</t>
+          <t>ZAIDANI ALI</t>
         </is>
       </c>
       <c r="C174" s="7" t="inlineStr">
@@ -10876,7 +10876,7 @@
         </is>
       </c>
       <c r="E174" s="8" t="n">
-        <v>-468398.13</v>
+        <v>-12329618.11</v>
       </c>
       <c r="F174" s="8" t="n">
         <v>0</v>
@@ -10892,12 +10892,12 @@
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>AC344</t>
+          <t>AC341</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>BAKHA MOKHTAR</t>
+          <t>HADDAD KHELLAF</t>
         </is>
       </c>
       <c r="C175" s="7" t="inlineStr">
@@ -10911,7 +10911,7 @@
         </is>
       </c>
       <c r="E175" s="8" t="n">
-        <v>-7587989.13</v>
+        <v>-2072726.88</v>
       </c>
       <c r="F175" s="8" t="n">
         <v>0</v>
@@ -10927,12 +10927,12 @@
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>AC345</t>
+          <t>AC343</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>SAIT ABDESLAM</t>
+          <t>YAKOUBI MEZIANE</t>
         </is>
       </c>
       <c r="C176" s="7" t="inlineStr">
@@ -10946,7 +10946,7 @@
         </is>
       </c>
       <c r="E176" s="8" t="n">
-        <v>-1686508.35</v>
+        <v>-468398.13</v>
       </c>
       <c r="F176" s="8" t="n">
         <v>0</v>
@@ -10962,12 +10962,12 @@
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>AC346</t>
+          <t>AC344</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>BOUKAIBA FAHEM</t>
+          <t>BAKHA MOKHTAR</t>
         </is>
       </c>
       <c r="C177" s="7" t="inlineStr">
@@ -10981,7 +10981,7 @@
         </is>
       </c>
       <c r="E177" s="8" t="n">
-        <v>-500000</v>
+        <v>-7587989.13</v>
       </c>
       <c r="F177" s="8" t="n">
         <v>0</v>
@@ -10997,12 +10997,12 @@
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>AC347</t>
+          <t>AC345</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>DJOUDI AMAR</t>
+          <t>SAIT ABDESLAM</t>
         </is>
       </c>
       <c r="C178" s="7" t="inlineStr">
@@ -11016,7 +11016,7 @@
         </is>
       </c>
       <c r="E178" s="8" t="n">
-        <v>-700068.67</v>
+        <v>-1686508.35</v>
       </c>
       <c r="F178" s="8" t="n">
         <v>0</v>
@@ -11032,12 +11032,12 @@
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>AC349</t>
+          <t>AC346</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>HARBIL LAID</t>
+          <t>BOUKAIBA FAHEM</t>
         </is>
       </c>
       <c r="C179" s="7" t="inlineStr">
@@ -11051,7 +11051,7 @@
         </is>
       </c>
       <c r="E179" s="8" t="n">
-        <v>-770000</v>
+        <v>-500000</v>
       </c>
       <c r="F179" s="8" t="n">
         <v>0</v>
@@ -11067,12 +11067,12 @@
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>AC350</t>
+          <t>AC347</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>MAZOUZ HACENE</t>
+          <t>DJOUDI AMAR</t>
         </is>
       </c>
       <c r="C180" s="7" t="inlineStr">
@@ -11086,7 +11086,7 @@
         </is>
       </c>
       <c r="E180" s="8" t="n">
-        <v>-480000</v>
+        <v>-700068.67</v>
       </c>
       <c r="F180" s="8" t="n">
         <v>0</v>
@@ -11102,12 +11102,12 @@
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>AC351</t>
+          <t>AC349</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>SELLAH BACHIR</t>
+          <t>HARBIL LAID</t>
         </is>
       </c>
       <c r="C181" s="7" t="inlineStr">
@@ -11121,7 +11121,7 @@
         </is>
       </c>
       <c r="E181" s="8" t="n">
-        <v>-1359375.23</v>
+        <v>-770000</v>
       </c>
       <c r="F181" s="8" t="n">
         <v>0</v>
@@ -11137,12 +11137,12 @@
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>AC352</t>
+          <t>AC350</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>MELIZOU LYES</t>
+          <t>MAZOUZ HACENE</t>
         </is>
       </c>
       <c r="C182" s="7" t="inlineStr">
@@ -11156,7 +11156,7 @@
         </is>
       </c>
       <c r="E182" s="8" t="n">
-        <v>-814164.92</v>
+        <v>-480000</v>
       </c>
       <c r="F182" s="8" t="n">
         <v>0</v>
@@ -11172,12 +11172,12 @@
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>AC353</t>
+          <t>AC351</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>BELFADEL MALIK</t>
+          <t>SELLAH BACHIR</t>
         </is>
       </c>
       <c r="C183" s="7" t="inlineStr">
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="E183" s="8" t="n">
-        <v>-1326085.76</v>
+        <v>-1359375.23</v>
       </c>
       <c r="F183" s="8" t="n">
         <v>0</v>
@@ -11207,12 +11207,12 @@
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>AC354</t>
+          <t>AC352</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>AIT YATA FARES</t>
+          <t>MELIZOU LYES</t>
         </is>
       </c>
       <c r="C184" s="7" t="inlineStr">
@@ -11226,7 +11226,7 @@
         </is>
       </c>
       <c r="E184" s="8" t="n">
-        <v>-500000</v>
+        <v>-814164.92</v>
       </c>
       <c r="F184" s="8" t="n">
         <v>0</v>
@@ -11242,12 +11242,12 @@
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>AC355</t>
+          <t>AC353</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>AMEUR KHELLAF</t>
+          <t>BELFADEL MALIK</t>
         </is>
       </c>
       <c r="C185" s="7" t="inlineStr">
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="E185" s="8" t="n">
-        <v>-11034657.94</v>
+        <v>-1326085.76</v>
       </c>
       <c r="F185" s="8" t="n">
         <v>0</v>
@@ -11277,12 +11277,12 @@
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t>AC357</t>
+          <t>AC354</t>
         </is>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>YAHIAOUI ELKHIYER</t>
+          <t>AIT YATA FARES</t>
         </is>
       </c>
       <c r="C186" s="7" t="inlineStr">
@@ -11296,7 +11296,7 @@
         </is>
       </c>
       <c r="E186" s="8" t="n">
-        <v>-51500</v>
+        <v>-500000</v>
       </c>
       <c r="F186" s="8" t="n">
         <v>0</v>
@@ -11312,12 +11312,12 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>AC358</t>
+          <t>AC355</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>IDIRI FAYCAL</t>
+          <t>AMEUR KHELLAF</t>
         </is>
       </c>
       <c r="C187" s="7" t="inlineStr">
@@ -11331,7 +11331,7 @@
         </is>
       </c>
       <c r="E187" s="8" t="n">
-        <v>-9000</v>
+        <v>-11034657.94</v>
       </c>
       <c r="F187" s="8" t="n">
         <v>0</v>
@@ -11347,12 +11347,12 @@
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>AC359</t>
+          <t>AC357</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>KADI MOHAND AREZKI</t>
+          <t>YAHIAOUI ELKHIYER</t>
         </is>
       </c>
       <c r="C188" s="7" t="inlineStr">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="E188" s="8" t="n">
-        <v>-4333712.42</v>
+        <v>-51500</v>
       </c>
       <c r="F188" s="8" t="n">
         <v>0</v>
@@ -11382,12 +11382,12 @@
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>AC360</t>
+          <t>AC358</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>SARL FATRASKI</t>
+          <t>IDIRI FAYCAL</t>
         </is>
       </c>
       <c r="C189" s="7" t="inlineStr">
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="E189" s="8" t="n">
-        <v>-351000</v>
+        <v>-9000</v>
       </c>
       <c r="F189" s="8" t="n">
         <v>0</v>
@@ -11417,12 +11417,12 @@
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>AC361</t>
+          <t>AC359</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>BENZIOUCHE THAMEUR</t>
+          <t>KADI MOHAND AREZKI</t>
         </is>
       </c>
       <c r="C190" s="7" t="inlineStr">
@@ -11436,7 +11436,7 @@
         </is>
       </c>
       <c r="E190" s="8" t="n">
-        <v>-183400</v>
+        <v>-4333712.42</v>
       </c>
       <c r="F190" s="8" t="n">
         <v>0</v>
@@ -11452,12 +11452,12 @@
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>AC362</t>
+          <t>AC360</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>YOUBI NACER EDDINE</t>
+          <t>SARL FATRASKI</t>
         </is>
       </c>
       <c r="C191" s="7" t="inlineStr">
@@ -11471,7 +11471,7 @@
         </is>
       </c>
       <c r="E191" s="8" t="n">
-        <v>-1185856.04</v>
+        <v>-351000</v>
       </c>
       <c r="F191" s="8" t="n">
         <v>0</v>
@@ -11487,12 +11487,12 @@
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>AC363</t>
+          <t>AC361</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>GHERIS MAHMOUD</t>
+          <t>BENZIOUCHE THAMEUR</t>
         </is>
       </c>
       <c r="C192" s="7" t="inlineStr">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E192" s="8" t="n">
-        <v>-700000</v>
+        <v>-183400</v>
       </c>
       <c r="F192" s="8" t="n">
         <v>0</v>
@@ -11522,12 +11522,12 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>AC364</t>
+          <t>AC362</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>IDIR MOULOUD</t>
+          <t>YOUBI NACER EDDINE</t>
         </is>
       </c>
       <c r="C193" s="7" t="inlineStr">
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="E193" s="8" t="n">
-        <v>-802553.67</v>
+        <v>-1185856.04</v>
       </c>
       <c r="F193" s="8" t="n">
         <v>0</v>
@@ -11557,12 +11557,12 @@
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t>AC366</t>
+          <t>AC363</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>SNC OUAMRI ET FILS</t>
+          <t>GHERIS MAHMOUD</t>
         </is>
       </c>
       <c r="C194" s="7" t="inlineStr">
@@ -11576,7 +11576,7 @@
         </is>
       </c>
       <c r="E194" s="8" t="n">
-        <v>-130000</v>
+        <v>-700000</v>
       </c>
       <c r="F194" s="8" t="n">
         <v>0</v>
@@ -11592,12 +11592,12 @@
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>AC368</t>
+          <t>AC364</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>BENBERNOU MOHAMED</t>
+          <t>IDIR MOULOUD</t>
         </is>
       </c>
       <c r="C195" s="7" t="inlineStr">
@@ -11611,7 +11611,7 @@
         </is>
       </c>
       <c r="E195" s="8" t="n">
-        <v>-300000</v>
+        <v>-802553.67</v>
       </c>
       <c r="F195" s="8" t="n">
         <v>0</v>
@@ -11627,12 +11627,12 @@
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>AC369</t>
+          <t>AC366</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>SARL TERGOU  M/CONSTRUCTIONS</t>
+          <t>SNC OUAMRI ET FILS</t>
         </is>
       </c>
       <c r="C196" s="7" t="inlineStr">
@@ -11646,7 +11646,7 @@
         </is>
       </c>
       <c r="E196" s="8" t="n">
-        <v>-490000</v>
+        <v>-130000</v>
       </c>
       <c r="F196" s="8" t="n">
         <v>0</v>
@@ -11662,12 +11662,12 @@
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>AC370</t>
+          <t>AC368</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>CHEBAH ABDESSALEM</t>
+          <t>BENBERNOU MOHAMED</t>
         </is>
       </c>
       <c r="C197" s="7" t="inlineStr">
@@ -11681,7 +11681,7 @@
         </is>
       </c>
       <c r="E197" s="8" t="n">
-        <v>-3400200</v>
+        <v>-300000</v>
       </c>
       <c r="F197" s="8" t="n">
         <v>0</v>
@@ -11697,12 +11697,12 @@
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t>AC371</t>
+          <t>AC369</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>BOUCHLAGHEM LYES</t>
+          <t>SARL TERGOU  M/CONSTRUCTIONS</t>
         </is>
       </c>
       <c r="C198" s="7" t="inlineStr">
@@ -11716,7 +11716,7 @@
         </is>
       </c>
       <c r="E198" s="8" t="n">
-        <v>-810388.17</v>
+        <v>-490000</v>
       </c>
       <c r="F198" s="8" t="n">
         <v>0</v>
@@ -11732,12 +11732,12 @@
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t>AC372</t>
+          <t>AC370</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>IDIR TOUFIK</t>
+          <t>CHEBAH ABDESSALEM</t>
         </is>
       </c>
       <c r="C199" s="7" t="inlineStr">
@@ -11751,7 +11751,7 @@
         </is>
       </c>
       <c r="E199" s="8" t="n">
-        <v>-530808.99</v>
+        <v>-3400200</v>
       </c>
       <c r="F199" s="8" t="n">
         <v>0</v>
@@ -11767,12 +11767,12 @@
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t>AC373</t>
+          <t>AC371</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>BENMEZIANE ABBAS</t>
+          <t>BOUCHLAGHEM LYES</t>
         </is>
       </c>
       <c r="C200" s="7" t="inlineStr">
@@ -11786,7 +11786,7 @@
         </is>
       </c>
       <c r="E200" s="8" t="n">
-        <v>-3133434.14</v>
+        <v>-810388.17</v>
       </c>
       <c r="F200" s="8" t="n">
         <v>0</v>
@@ -11802,12 +11802,12 @@
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>AC374</t>
+          <t>AC372</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>EURL BIZIOU</t>
+          <t>IDIR TOUFIK</t>
         </is>
       </c>
       <c r="C201" s="7" t="inlineStr">
@@ -11821,7 +11821,7 @@
         </is>
       </c>
       <c r="E201" s="8" t="n">
-        <v>-4168226.83</v>
+        <v>-530808.99</v>
       </c>
       <c r="F201" s="8" t="n">
         <v>0</v>
@@ -11837,12 +11837,12 @@
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t>AC375</t>
+          <t>AC373</t>
         </is>
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>KEZIZ KHALED</t>
+          <t>BENMEZIANE ABBAS</t>
         </is>
       </c>
       <c r="C202" s="7" t="inlineStr">
@@ -11856,7 +11856,7 @@
         </is>
       </c>
       <c r="E202" s="8" t="n">
-        <v>-518874.41</v>
+        <v>-3133434.14</v>
       </c>
       <c r="F202" s="8" t="n">
         <v>0</v>
@@ -11872,12 +11872,12 @@
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>AC376</t>
+          <t>AC374</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>FERHAT SAMIR</t>
+          <t>EURL BIZIOU</t>
         </is>
       </c>
       <c r="C203" s="7" t="inlineStr">
@@ -11891,7 +11891,7 @@
         </is>
       </c>
       <c r="E203" s="8" t="n">
-        <v>-1302896.83</v>
+        <v>-4168226.83</v>
       </c>
       <c r="F203" s="8" t="n">
         <v>0</v>
@@ -11907,12 +11907,12 @@
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t>AC377</t>
+          <t>AC375</t>
         </is>
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>FERROUDJ REDOUANE</t>
+          <t>KEZIZ KHALED</t>
         </is>
       </c>
       <c r="C204" s="7" t="inlineStr">
@@ -11926,7 +11926,7 @@
         </is>
       </c>
       <c r="E204" s="8" t="n">
-        <v>-1100454.46</v>
+        <v>-518874.41</v>
       </c>
       <c r="F204" s="8" t="n">
         <v>0</v>
@@ -11942,12 +11942,12 @@
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>AC378</t>
+          <t>AC376</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>BENYAHIA AMAR</t>
+          <t>FERHAT SAMIR</t>
         </is>
       </c>
       <c r="C205" s="7" t="inlineStr">
@@ -11961,7 +11961,7 @@
         </is>
       </c>
       <c r="E205" s="8" t="n">
-        <v>-313100</v>
+        <v>-1302896.83</v>
       </c>
       <c r="F205" s="8" t="n">
         <v>0</v>
@@ -11977,12 +11977,12 @@
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
         <is>
-          <t>AC379</t>
+          <t>AC377</t>
         </is>
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>BENDAHMANE LHACHEMI</t>
+          <t>FERROUDJ REDOUANE</t>
         </is>
       </c>
       <c r="C206" s="7" t="inlineStr">
@@ -11996,7 +11996,7 @@
         </is>
       </c>
       <c r="E206" s="8" t="n">
-        <v>-906661.23</v>
+        <v>-1100454.46</v>
       </c>
       <c r="F206" s="8" t="n">
         <v>0</v>
@@ -12012,12 +12012,12 @@
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>AC380</t>
+          <t>AC378</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>BENHAMA TAHAR</t>
+          <t>BENYAHIA AMAR</t>
         </is>
       </c>
       <c r="C207" s="7" t="inlineStr">
@@ -12031,7 +12031,7 @@
         </is>
       </c>
       <c r="E207" s="8" t="n">
-        <v>-308338.53</v>
+        <v>-313100</v>
       </c>
       <c r="F207" s="8" t="n">
         <v>0</v>
@@ -12047,12 +12047,12 @@
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>AC381</t>
+          <t>AC379</t>
         </is>
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>SARL SIARI MEHLIA TPP</t>
+          <t>BENDAHMANE LHACHEMI</t>
         </is>
       </c>
       <c r="C208" s="7" t="inlineStr">
@@ -12066,7 +12066,7 @@
         </is>
       </c>
       <c r="E208" s="8" t="n">
-        <v>-2162328.3</v>
+        <v>-906661.23</v>
       </c>
       <c r="F208" s="8" t="n">
         <v>0</v>
@@ -12082,12 +12082,12 @@
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>AC382</t>
+          <t>AC380</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>IGHEMOURACENE SALAH</t>
+          <t>BENHAMA TAHAR</t>
         </is>
       </c>
       <c r="C209" s="7" t="inlineStr">
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="E209" s="8" t="n">
-        <v>-100000</v>
+        <v>-308338.53</v>
       </c>
       <c r="F209" s="8" t="n">
         <v>0</v>
@@ -12117,12 +12117,12 @@
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
         <is>
-          <t>AC383</t>
+          <t>AC381</t>
         </is>
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>SNC L'AIGLE DES COLINES</t>
+          <t>SARL SIARI MEHLIA TPP</t>
         </is>
       </c>
       <c r="C210" s="7" t="inlineStr">
@@ -12136,7 +12136,7 @@
         </is>
       </c>
       <c r="E210" s="8" t="n">
-        <v>-7453500.71</v>
+        <v>-2162328.3</v>
       </c>
       <c r="F210" s="8" t="n">
         <v>0</v>
@@ -12152,12 +12152,12 @@
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>AC384</t>
+          <t>AC382</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>LOUALI MOHAMED</t>
+          <t>IGHEMOURACENE SALAH</t>
         </is>
       </c>
       <c r="C211" s="7" t="inlineStr">
@@ -12171,7 +12171,7 @@
         </is>
       </c>
       <c r="E211" s="8" t="n">
-        <v>-401200</v>
+        <v>-100000</v>
       </c>
       <c r="F211" s="8" t="n">
         <v>0</v>
@@ -12187,12 +12187,12 @@
     <row r="212">
       <c r="A212" s="7" t="inlineStr">
         <is>
-          <t>AC385</t>
+          <t>AC383</t>
         </is>
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>NAFTAL GPL SAIDA</t>
+          <t>SNC L'AIGLE DES COLINES</t>
         </is>
       </c>
       <c r="C212" s="7" t="inlineStr">
@@ -12206,7 +12206,7 @@
         </is>
       </c>
       <c r="E212" s="8" t="n">
-        <v>-395318</v>
+        <v>-7453500.71</v>
       </c>
       <c r="F212" s="8" t="n">
         <v>0</v>
@@ -12222,12 +12222,12 @@
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>AC387</t>
+          <t>AC384</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>SLIMANI MOULOUD</t>
+          <t>LOUALI MOHAMED</t>
         </is>
       </c>
       <c r="C213" s="7" t="inlineStr">
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="E213" s="8" t="n">
-        <v>-4000</v>
+        <v>-401200</v>
       </c>
       <c r="F213" s="8" t="n">
         <v>0</v>
@@ -12257,12 +12257,12 @@
     <row r="214">
       <c r="A214" s="7" t="inlineStr">
         <is>
-          <t>AC389</t>
+          <t>AC385</t>
         </is>
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>MANSOURI ZOUBIR</t>
+          <t>NAFTAL GPL SAIDA</t>
         </is>
       </c>
       <c r="C214" s="7" t="inlineStr">
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="E214" s="8" t="n">
-        <v>-9254548</v>
+        <v>-395318</v>
       </c>
       <c r="F214" s="8" t="n">
         <v>0</v>
@@ -12292,12 +12292,12 @@
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>AC390</t>
+          <t>AC387</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>SELLAH AKLI</t>
+          <t>SLIMANI MOULOUD</t>
         </is>
       </c>
       <c r="C215" s="7" t="inlineStr">
@@ -12311,7 +12311,7 @@
         </is>
       </c>
       <c r="E215" s="8" t="n">
-        <v>-3702637.99</v>
+        <v>-4000</v>
       </c>
       <c r="F215" s="8" t="n">
         <v>0</v>
@@ -12327,12 +12327,12 @@
     <row r="216">
       <c r="A216" s="7" t="inlineStr">
         <is>
-          <t>AC391</t>
+          <t>AC389</t>
         </is>
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>IDIR NADIR</t>
+          <t>MANSOURI ZOUBIR</t>
         </is>
       </c>
       <c r="C216" s="7" t="inlineStr">
@@ -12346,7 +12346,7 @@
         </is>
       </c>
       <c r="E216" s="8" t="n">
-        <v>-1537954.06</v>
+        <v>-9254548</v>
       </c>
       <c r="F216" s="8" t="n">
         <v>0</v>
@@ -12362,12 +12362,12 @@
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>AC392</t>
+          <t>AC390</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>BOUAMAR HAKIM</t>
+          <t>SELLAH AKLI</t>
         </is>
       </c>
       <c r="C217" s="7" t="inlineStr">
@@ -12381,7 +12381,7 @@
         </is>
       </c>
       <c r="E217" s="8" t="n">
-        <v>-917300</v>
+        <v>-3702637.99</v>
       </c>
       <c r="F217" s="8" t="n">
         <v>0</v>
@@ -12397,12 +12397,12 @@
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
         <is>
-          <t>AC393</t>
+          <t>AC391</t>
         </is>
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>SELLAH NOUREDINE</t>
+          <t>IDIR NADIR</t>
         </is>
       </c>
       <c r="C218" s="7" t="inlineStr">
@@ -12416,7 +12416,7 @@
         </is>
       </c>
       <c r="E218" s="8" t="n">
-        <v>-504755.04</v>
+        <v>-1537954.06</v>
       </c>
       <c r="F218" s="8" t="n">
         <v>0</v>
@@ -12432,12 +12432,12 @@
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>AC394</t>
+          <t>AC392</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t>FERHAT SALIM</t>
+          <t>BOUAMAR HAKIM</t>
         </is>
       </c>
       <c r="C219" s="7" t="inlineStr">
@@ -12451,7 +12451,7 @@
         </is>
       </c>
       <c r="E219" s="8" t="n">
-        <v>-1600000</v>
+        <v>-917300</v>
       </c>
       <c r="F219" s="8" t="n">
         <v>0</v>
@@ -12467,12 +12467,12 @@
     <row r="220">
       <c r="A220" s="7" t="inlineStr">
         <is>
-          <t>AC395</t>
+          <t>AC393</t>
         </is>
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>SELLAH SALIM</t>
+          <t>SELLAH NOUREDINE</t>
         </is>
       </c>
       <c r="C220" s="7" t="inlineStr">
@@ -12486,7 +12486,7 @@
         </is>
       </c>
       <c r="E220" s="8" t="n">
-        <v>-650000</v>
+        <v>-504755.04</v>
       </c>
       <c r="F220" s="8" t="n">
         <v>0</v>
@@ -12502,12 +12502,12 @@
     <row r="221">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>AC396</t>
+          <t>AC394</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>BIBI SMAIL</t>
+          <t>FERHAT SALIM</t>
         </is>
       </c>
       <c r="C221" s="7" t="inlineStr">
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="E221" s="8" t="n">
-        <v>-3702000</v>
+        <v>-1600000</v>
       </c>
       <c r="F221" s="8" t="n">
         <v>0</v>
@@ -12537,12 +12537,12 @@
     <row r="222">
       <c r="A222" s="7" t="inlineStr">
         <is>
-          <t>AC397</t>
+          <t>AC395</t>
         </is>
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>SELLAH SALAH</t>
+          <t>SELLAH SALIM</t>
         </is>
       </c>
       <c r="C222" s="7" t="inlineStr">
@@ -12556,7 +12556,7 @@
         </is>
       </c>
       <c r="E222" s="8" t="n">
-        <v>-820063.63</v>
+        <v>-650000</v>
       </c>
       <c r="F222" s="8" t="n">
         <v>0</v>
@@ -12572,12 +12572,12 @@
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>AC398</t>
+          <t>AC396</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>IMEDNI TARIK</t>
+          <t>BIBI SMAIL</t>
         </is>
       </c>
       <c r="C223" s="7" t="inlineStr">
@@ -12591,7 +12591,7 @@
         </is>
       </c>
       <c r="E223" s="8" t="n">
-        <v>-1288597.98</v>
+        <v>-3702000</v>
       </c>
       <c r="F223" s="8" t="n">
         <v>0</v>
@@ -12607,12 +12607,12 @@
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
         <is>
-          <t>AC399</t>
+          <t>AC397</t>
         </is>
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>AIT KHEDACHE FAHIM</t>
+          <t>SELLAH SALAH</t>
         </is>
       </c>
       <c r="C224" s="7" t="inlineStr">
@@ -12626,7 +12626,7 @@
         </is>
       </c>
       <c r="E224" s="8" t="n">
-        <v>-1018231.82</v>
+        <v>-820063.63</v>
       </c>
       <c r="F224" s="8" t="n">
         <v>0</v>
@@ -12642,12 +12642,12 @@
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>AC400</t>
+          <t>AC398</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>LOUANAS AMAR</t>
+          <t>IMEDNI TARIK</t>
         </is>
       </c>
       <c r="C225" s="7" t="inlineStr">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="E225" s="8" t="n">
-        <v>-753731.7</v>
+        <v>-1288597.98</v>
       </c>
       <c r="F225" s="8" t="n">
         <v>0</v>
@@ -12677,12 +12677,12 @@
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
         <is>
-          <t>AC402</t>
+          <t>AC399</t>
         </is>
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>SAIDOUN YACINE</t>
+          <t>AIT KHEDACHE FAHIM</t>
         </is>
       </c>
       <c r="C226" s="7" t="inlineStr">
@@ -12696,7 +12696,7 @@
         </is>
       </c>
       <c r="E226" s="8" t="n">
-        <v>-9857236.42</v>
+        <v>-1018231.82</v>
       </c>
       <c r="F226" s="8" t="n">
         <v>0</v>
@@ -12712,12 +12712,12 @@
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>AC403</t>
+          <t>AC400</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
-          <t>SNC LTNC NAOUI ET CIE</t>
+          <t>LOUANAS AMAR</t>
         </is>
       </c>
       <c r="C227" s="7" t="inlineStr">
@@ -12731,7 +12731,7 @@
         </is>
       </c>
       <c r="E227" s="8" t="n">
-        <v>-1002150.73</v>
+        <v>-753731.7</v>
       </c>
       <c r="F227" s="8" t="n">
         <v>0</v>
@@ -12747,12 +12747,12 @@
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
-          <t>AC404</t>
+          <t>AC402</t>
         </is>
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>LARABI MADJID</t>
+          <t>SAIDOUN YACINE</t>
         </is>
       </c>
       <c r="C228" s="7" t="inlineStr">
@@ -12766,7 +12766,7 @@
         </is>
       </c>
       <c r="E228" s="8" t="n">
-        <v>-1347114.28</v>
+        <v>-9857236.42</v>
       </c>
       <c r="F228" s="8" t="n">
         <v>0</v>
@@ -12782,12 +12782,12 @@
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>AC405</t>
+          <t>AC403</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
-          <t>BOUKELA MADJID</t>
+          <t>SNC LTNC NAOUI ET CIE</t>
         </is>
       </c>
       <c r="C229" s="7" t="inlineStr">
@@ -12801,7 +12801,7 @@
         </is>
       </c>
       <c r="E229" s="8" t="n">
-        <v>-1500000</v>
+        <v>-1002150.73</v>
       </c>
       <c r="F229" s="8" t="n">
         <v>0</v>
@@ -12817,12 +12817,12 @@
     <row r="230">
       <c r="A230" s="7" t="inlineStr">
         <is>
-          <t>AC406</t>
+          <t>AC404</t>
         </is>
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>ATHMANE ABDELLAH</t>
+          <t>LARABI MADJID</t>
         </is>
       </c>
       <c r="C230" s="7" t="inlineStr">
@@ -12836,7 +12836,7 @@
         </is>
       </c>
       <c r="E230" s="8" t="n">
-        <v>-584760</v>
+        <v>-1347114.28</v>
       </c>
       <c r="F230" s="8" t="n">
         <v>0</v>
@@ -12852,12 +12852,12 @@
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>AC407</t>
+          <t>AC405</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
         <is>
-          <t>CHAABNA SLIMANE</t>
+          <t>BOUKELA MADJID</t>
         </is>
       </c>
       <c r="C231" s="7" t="inlineStr">
@@ -12871,7 +12871,7 @@
         </is>
       </c>
       <c r="E231" s="8" t="n">
-        <v>-541673.92</v>
+        <v>-1500000</v>
       </c>
       <c r="F231" s="8" t="n">
         <v>0</v>
@@ -12887,12 +12887,12 @@
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
         <is>
-          <t>AC408</t>
+          <t>AC406</t>
         </is>
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>LAMINE YOUCEF</t>
+          <t>ATHMANE ABDELLAH</t>
         </is>
       </c>
       <c r="C232" s="7" t="inlineStr">
@@ -12906,7 +12906,7 @@
         </is>
       </c>
       <c r="E232" s="8" t="n">
-        <v>-198326.8</v>
+        <v>-584760</v>
       </c>
       <c r="F232" s="8" t="n">
         <v>0</v>
@@ -12922,12 +12922,12 @@
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>AC409</t>
+          <t>AC407</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t>EURL BENYAHIA CARRIERE</t>
+          <t>CHAABNA SLIMANE</t>
         </is>
       </c>
       <c r="C233" s="7" t="inlineStr">
@@ -12941,7 +12941,7 @@
         </is>
       </c>
       <c r="E233" s="8" t="n">
-        <v>-800000</v>
+        <v>-541673.92</v>
       </c>
       <c r="F233" s="8" t="n">
         <v>0</v>
@@ -12957,12 +12957,12 @@
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
         <is>
-          <t>AC410</t>
+          <t>AC408</t>
         </is>
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>BECHRI FAYSSAL</t>
+          <t>LAMINE YOUCEF</t>
         </is>
       </c>
       <c r="C234" s="7" t="inlineStr">
@@ -12976,7 +12976,7 @@
         </is>
       </c>
       <c r="E234" s="8" t="n">
-        <v>-208260.39</v>
+        <v>-198326.8</v>
       </c>
       <c r="F234" s="8" t="n">
         <v>0</v>
@@ -12992,12 +12992,12 @@
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>AC411</t>
+          <t>AC409</t>
         </is>
       </c>
       <c r="B235" s="6" t="inlineStr">
         <is>
-          <t>SALHI OUALI</t>
+          <t>EURL BENYAHIA CARRIERE</t>
         </is>
       </c>
       <c r="C235" s="7" t="inlineStr">
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="E235" s="8" t="n">
-        <v>-210471.27</v>
+        <v>-800000</v>
       </c>
       <c r="F235" s="8" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
     <row r="236">
       <c r="A236" s="7" t="inlineStr">
         <is>
-          <t>AC412</t>
+          <t>AC410</t>
         </is>
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>SALMI ABDESLAM</t>
+          <t>BECHRI FAYSSAL</t>
         </is>
       </c>
       <c r="C236" s="7" t="inlineStr">
@@ -13046,7 +13046,7 @@
         </is>
       </c>
       <c r="E236" s="8" t="n">
-        <v>-200000</v>
+        <v>-208260.39</v>
       </c>
       <c r="F236" s="8" t="n">
         <v>0</v>
@@ -13062,12 +13062,12 @@
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>AC413</t>
+          <t>AC411</t>
         </is>
       </c>
       <c r="B237" s="6" t="inlineStr">
         <is>
-          <t>ABDOUNE RAFIK</t>
+          <t>SALHI OUALI</t>
         </is>
       </c>
       <c r="C237" s="7" t="inlineStr">
@@ -13081,7 +13081,7 @@
         </is>
       </c>
       <c r="E237" s="8" t="n">
-        <v>-435515.5</v>
+        <v>-210471.27</v>
       </c>
       <c r="F237" s="8" t="n">
         <v>0</v>
@@ -13097,12 +13097,12 @@
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
         <is>
-          <t>AC414</t>
+          <t>AC412</t>
         </is>
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>FERTAL LYAZID</t>
+          <t>SALMI ABDESLAM</t>
         </is>
       </c>
       <c r="C238" s="7" t="inlineStr">
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="E238" s="8" t="n">
-        <v>-655410.28</v>
+        <v>-200000</v>
       </c>
       <c r="F238" s="8" t="n">
         <v>0</v>
@@ -13132,12 +13132,12 @@
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>AC415</t>
+          <t>AC413</t>
         </is>
       </c>
       <c r="B239" s="6" t="inlineStr">
         <is>
-          <t>MEHDAOUI SAID</t>
+          <t>ABDOUNE RAFIK</t>
         </is>
       </c>
       <c r="C239" s="7" t="inlineStr">
@@ -13151,7 +13151,7 @@
         </is>
       </c>
       <c r="E239" s="8" t="n">
-        <v>-2069100</v>
+        <v>-435515.5</v>
       </c>
       <c r="F239" s="8" t="n">
         <v>0</v>
@@ -13167,12 +13167,12 @@
     <row r="240">
       <c r="A240" s="7" t="inlineStr">
         <is>
-          <t>AC416</t>
+          <t>AC414</t>
         </is>
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>TEI ABDELFATAH</t>
+          <t>FERTAL LYAZID</t>
         </is>
       </c>
       <c r="C240" s="7" t="inlineStr">
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="E240" s="8" t="n">
-        <v>-1399999.98</v>
+        <v>-655410.28</v>
       </c>
       <c r="F240" s="8" t="n">
         <v>0</v>
@@ -13202,12 +13202,12 @@
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>AC417</t>
+          <t>AC415</t>
         </is>
       </c>
       <c r="B241" s="6" t="inlineStr">
         <is>
-          <t>KERKADENE AMAR</t>
+          <t>MEHDAOUI SAID</t>
         </is>
       </c>
       <c r="C241" s="7" t="inlineStr">
@@ -13221,7 +13221,7 @@
         </is>
       </c>
       <c r="E241" s="8" t="n">
-        <v>-480000</v>
+        <v>-2069100</v>
       </c>
       <c r="F241" s="8" t="n">
         <v>0</v>
@@ -13237,12 +13237,12 @@
     <row r="242">
       <c r="A242" s="7" t="inlineStr">
         <is>
-          <t>AC418</t>
+          <t>AC416</t>
         </is>
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>SARL BOUKOUCHA SABL OUED AGRIO</t>
+          <t>TEI ABDELFATAH</t>
         </is>
       </c>
       <c r="C242" s="7" t="inlineStr">
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="E242" s="8" t="n">
-        <v>-580400</v>
+        <v>-1399999.98</v>
       </c>
       <c r="F242" s="8" t="n">
         <v>0</v>
@@ -13272,12 +13272,12 @@
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>AC423</t>
+          <t>AC417</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
         <is>
-          <t>DJOUMI LOUNES</t>
+          <t>KERKADENE AMAR</t>
         </is>
       </c>
       <c r="C243" s="7" t="inlineStr">
@@ -13291,7 +13291,7 @@
         </is>
       </c>
       <c r="E243" s="8" t="n">
-        <v>-100000</v>
+        <v>-480000</v>
       </c>
       <c r="F243" s="8" t="n">
         <v>0</v>
@@ -13307,12 +13307,12 @@
     <row r="244">
       <c r="A244" s="7" t="inlineStr">
         <is>
-          <t>AC427</t>
+          <t>AC418</t>
         </is>
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>EURL NET TRANSPORT</t>
+          <t>SARL BOUKOUCHA SABL OUED AGRIO</t>
         </is>
       </c>
       <c r="C244" s="7" t="inlineStr">
@@ -13326,7 +13326,7 @@
         </is>
       </c>
       <c r="E244" s="8" t="n">
-        <v>-1187441.5</v>
+        <v>-580400</v>
       </c>
       <c r="F244" s="8" t="n">
         <v>0</v>
@@ -13342,12 +13342,12 @@
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
         <is>
-          <t>AC428</t>
+          <t>AC423</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
         <is>
-          <t>SARL TITOU TPM</t>
+          <t>DJOUMI LOUNES</t>
         </is>
       </c>
       <c r="C245" s="7" t="inlineStr">
@@ -13361,7 +13361,7 @@
         </is>
       </c>
       <c r="E245" s="8" t="n">
-        <v>-811721</v>
+        <v>-100000</v>
       </c>
       <c r="F245" s="8" t="n">
         <v>0</v>
@@ -13377,12 +13377,12 @@
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
         <is>
-          <t>AC429</t>
+          <t>AC427</t>
         </is>
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>SAIDANI HAMOU</t>
+          <t>EURL NET TRANSPORT</t>
         </is>
       </c>
       <c r="C246" s="7" t="inlineStr">
@@ -13396,7 +13396,7 @@
         </is>
       </c>
       <c r="E246" s="8" t="n">
-        <v>-351464.94</v>
+        <v>-1187441.5</v>
       </c>
       <c r="F246" s="8" t="n">
         <v>0</v>
@@ -13412,12 +13412,12 @@
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>AC430</t>
+          <t>AC428</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
         <is>
-          <t>ABDOUNE ABDENACER</t>
+          <t>SARL TITOU TPM</t>
         </is>
       </c>
       <c r="C247" s="7" t="inlineStr">
@@ -13431,7 +13431,7 @@
         </is>
       </c>
       <c r="E247" s="8" t="n">
-        <v>-250000</v>
+        <v>-811721</v>
       </c>
       <c r="F247" s="8" t="n">
         <v>0</v>
@@ -13447,12 +13447,12 @@
     <row r="248">
       <c r="A248" s="7" t="inlineStr">
         <is>
-          <t>AC431</t>
+          <t>AC429</t>
         </is>
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>AZZOUG FARID</t>
+          <t>SAIDANI HAMOU</t>
         </is>
       </c>
       <c r="C248" s="7" t="inlineStr">
@@ -13466,7 +13466,7 @@
         </is>
       </c>
       <c r="E248" s="8" t="n">
-        <v>-171149.59</v>
+        <v>-351464.94</v>
       </c>
       <c r="F248" s="8" t="n">
         <v>0</v>
@@ -13482,12 +13482,12 @@
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>AC433</t>
+          <t>AC430</t>
         </is>
       </c>
       <c r="B249" s="6" t="inlineStr">
         <is>
-          <t>DEROUICHE MAHMOUD</t>
+          <t>ABDOUNE ABDENACER</t>
         </is>
       </c>
       <c r="C249" s="7" t="inlineStr">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="E249" s="8" t="n">
-        <v>-766458.8100000001</v>
+        <v>-250000</v>
       </c>
       <c r="F249" s="8" t="n">
         <v>0</v>
@@ -13517,12 +13517,12 @@
     <row r="250">
       <c r="A250" s="7" t="inlineStr">
         <is>
-          <t>AC436</t>
+          <t>AC431</t>
         </is>
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>BENKHELIFA ABDELHAKIM</t>
+          <t>AZZOUG FARID</t>
         </is>
       </c>
       <c r="C250" s="7" t="inlineStr">
@@ -13536,7 +13536,7 @@
         </is>
       </c>
       <c r="E250" s="8" t="n">
-        <v>-60000</v>
+        <v>-171149.59</v>
       </c>
       <c r="F250" s="8" t="n">
         <v>0</v>
@@ -13552,12 +13552,12 @@
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>AC439</t>
+          <t>AC433</t>
         </is>
       </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
-          <t>AYACHI AMOR ABDELMALEK</t>
+          <t>DEROUICHE MAHMOUD</t>
         </is>
       </c>
       <c r="C251" s="7" t="inlineStr">
@@ -13571,7 +13571,7 @@
         </is>
       </c>
       <c r="E251" s="8" t="n">
-        <v>-315000</v>
+        <v>-766458.8100000001</v>
       </c>
       <c r="F251" s="8" t="n">
         <v>0</v>
@@ -13587,12 +13587,12 @@
     <row r="252">
       <c r="A252" s="7" t="inlineStr">
         <is>
-          <t>AC440</t>
+          <t>AC436</t>
         </is>
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>ZIANI AMIR</t>
+          <t>BENKHELIFA ABDELHAKIM</t>
         </is>
       </c>
       <c r="C252" s="7" t="inlineStr">
@@ -13606,7 +13606,7 @@
         </is>
       </c>
       <c r="E252" s="8" t="n">
-        <v>-250000</v>
+        <v>-60000</v>
       </c>
       <c r="F252" s="8" t="n">
         <v>0</v>
@@ -13622,12 +13622,12 @@
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
         <is>
-          <t>AC441</t>
+          <t>AC439</t>
         </is>
       </c>
       <c r="B253" s="6" t="inlineStr">
         <is>
-          <t>MADI KARIM</t>
+          <t>AYACHI AMOR ABDELMALEK</t>
         </is>
       </c>
       <c r="C253" s="7" t="inlineStr">
@@ -13641,7 +13641,7 @@
         </is>
       </c>
       <c r="E253" s="8" t="n">
-        <v>-1561986.88</v>
+        <v>-315000</v>
       </c>
       <c r="F253" s="8" t="n">
         <v>0</v>
@@ -13657,12 +13657,12 @@
     <row r="254">
       <c r="A254" s="7" t="inlineStr">
         <is>
-          <t>AC442</t>
+          <t>AC440</t>
         </is>
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>ETB TCE BOUHADJELA MOHAMED</t>
+          <t>ZIANI AMIR</t>
         </is>
       </c>
       <c r="C254" s="7" t="inlineStr">
@@ -13676,7 +13676,7 @@
         </is>
       </c>
       <c r="E254" s="8" t="n">
-        <v>-1000000</v>
+        <v>-250000</v>
       </c>
       <c r="F254" s="8" t="n">
         <v>0</v>
@@ -13692,12 +13692,12 @@
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
         <is>
-          <t>AC443</t>
+          <t>AC441</t>
         </is>
       </c>
       <c r="B255" s="6" t="inlineStr">
         <is>
-          <t>GASSA MOULOUD</t>
+          <t>MADI KARIM</t>
         </is>
       </c>
       <c r="C255" s="7" t="inlineStr">
@@ -13711,7 +13711,7 @@
         </is>
       </c>
       <c r="E255" s="8" t="n">
-        <v>-1291995.08</v>
+        <v>-1561986.88</v>
       </c>
       <c r="F255" s="8" t="n">
         <v>0</v>
@@ -13727,12 +13727,12 @@
     <row r="256">
       <c r="A256" s="7" t="inlineStr">
         <is>
-          <t>AC444</t>
+          <t>AC442</t>
         </is>
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>EURL ALL TRANSFERT</t>
+          <t>ETB TCE BOUHADJELA MOHAMED</t>
         </is>
       </c>
       <c r="C256" s="7" t="inlineStr">
@@ -13746,7 +13746,7 @@
         </is>
       </c>
       <c r="E256" s="8" t="n">
-        <v>-552778.74</v>
+        <v>-1000000</v>
       </c>
       <c r="F256" s="8" t="n">
         <v>0</v>
@@ -13762,12 +13762,12 @@
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>AC445</t>
+          <t>AC443</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
         <is>
-          <t>HARFOUCHE REDA</t>
+          <t>GASSA MOULOUD</t>
         </is>
       </c>
       <c r="C257" s="7" t="inlineStr">
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="E257" s="8" t="n">
-        <v>-1972018.2</v>
+        <v>-1291995.08</v>
       </c>
       <c r="F257" s="8" t="n">
         <v>0</v>
@@ -13797,12 +13797,12 @@
     <row r="258">
       <c r="A258" s="7" t="inlineStr">
         <is>
-          <t>AC446</t>
+          <t>AC444</t>
         </is>
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>AMEUR LAID</t>
+          <t>EURL ALL TRANSFERT</t>
         </is>
       </c>
       <c r="C258" s="7" t="inlineStr">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="E258" s="8" t="n">
-        <v>-1093000</v>
+        <v>-552778.74</v>
       </c>
       <c r="F258" s="8" t="n">
         <v>0</v>
@@ -13832,12 +13832,12 @@
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>AC447</t>
+          <t>AC445</t>
         </is>
       </c>
       <c r="B259" s="6" t="inlineStr">
         <is>
-          <t>DEHAM HOCINE</t>
+          <t>HARFOUCHE REDA</t>
         </is>
       </c>
       <c r="C259" s="7" t="inlineStr">
@@ -13851,7 +13851,7 @@
         </is>
       </c>
       <c r="E259" s="8" t="n">
-        <v>-429959.39</v>
+        <v>-1972018.2</v>
       </c>
       <c r="F259" s="8" t="n">
         <v>0</v>
@@ -13867,12 +13867,12 @@
     <row r="260">
       <c r="A260" s="7" t="inlineStr">
         <is>
-          <t>AC448</t>
+          <t>AC446</t>
         </is>
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>MEZIANE KHELIFA</t>
+          <t>AMEUR LAID</t>
         </is>
       </c>
       <c r="C260" s="7" t="inlineStr">
@@ -13886,7 +13886,7 @@
         </is>
       </c>
       <c r="E260" s="8" t="n">
-        <v>-500572.61</v>
+        <v>-1093000</v>
       </c>
       <c r="F260" s="8" t="n">
         <v>0</v>
@@ -13902,12 +13902,12 @@
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>AC449</t>
+          <t>AC447</t>
         </is>
       </c>
       <c r="B261" s="6" t="inlineStr">
         <is>
-          <t>YAHIAOUI ZAID</t>
+          <t>DEHAM HOCINE</t>
         </is>
       </c>
       <c r="C261" s="7" t="inlineStr">
@@ -13921,7 +13921,7 @@
         </is>
       </c>
       <c r="E261" s="8" t="n">
-        <v>-298900</v>
+        <v>-429959.39</v>
       </c>
       <c r="F261" s="8" t="n">
         <v>0</v>
@@ -13937,12 +13937,12 @@
     <row r="262">
       <c r="A262" s="7" t="inlineStr">
         <is>
-          <t>AC450</t>
+          <t>AC448</t>
         </is>
       </c>
       <c r="B262" s="6" t="inlineStr">
         <is>
-          <t>AIT ALI HICHAM DJAMEL PIECES</t>
+          <t>MEZIANE KHELIFA</t>
         </is>
       </c>
       <c r="C262" s="7" t="inlineStr">
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="E262" s="8" t="n">
-        <v>-400000</v>
+        <v>-500572.61</v>
       </c>
       <c r="F262" s="8" t="n">
         <v>0</v>
@@ -13972,12 +13972,12 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>AC451</t>
+          <t>AC449</t>
         </is>
       </c>
       <c r="B263" s="6" t="inlineStr">
         <is>
-          <t>IGOUCIMENE FAOUZI</t>
+          <t>YAHIAOUI ZAID</t>
         </is>
       </c>
       <c r="C263" s="7" t="inlineStr">
@@ -13991,7 +13991,7 @@
         </is>
       </c>
       <c r="E263" s="8" t="n">
-        <v>-598013.55</v>
+        <v>-298900</v>
       </c>
       <c r="F263" s="8" t="n">
         <v>0</v>
@@ -14007,12 +14007,12 @@
     <row r="264">
       <c r="A264" s="7" t="inlineStr">
         <is>
-          <t>AC452</t>
+          <t>AC450</t>
         </is>
       </c>
       <c r="B264" s="6" t="inlineStr">
         <is>
-          <t>KERROUCHE LYES</t>
+          <t>AIT ALI HICHAM DJAMEL PIECES</t>
         </is>
       </c>
       <c r="C264" s="7" t="inlineStr">
@@ -14026,7 +14026,7 @@
         </is>
       </c>
       <c r="E264" s="8" t="n">
-        <v>-924449.88</v>
+        <v>-400000</v>
       </c>
       <c r="F264" s="8" t="n">
         <v>0</v>
@@ -14042,12 +14042,12 @@
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>AC455</t>
+          <t>AC451</t>
         </is>
       </c>
       <c r="B265" s="6" t="inlineStr">
         <is>
-          <t>BENABAS FATEH</t>
+          <t>IGOUCIMENE FAOUZI</t>
         </is>
       </c>
       <c r="C265" s="7" t="inlineStr">
@@ -14061,7 +14061,7 @@
         </is>
       </c>
       <c r="E265" s="8" t="n">
-        <v>-802905.91</v>
+        <v>-598013.55</v>
       </c>
       <c r="F265" s="8" t="n">
         <v>0</v>
@@ -14077,12 +14077,12 @@
     <row r="266">
       <c r="A266" s="7" t="inlineStr">
         <is>
-          <t>AC457</t>
+          <t>AC452</t>
         </is>
       </c>
       <c r="B266" s="6" t="inlineStr">
         <is>
-          <t>MESSAST ABDELOUAHAB</t>
+          <t>KERROUCHE LYES</t>
         </is>
       </c>
       <c r="C266" s="7" t="inlineStr">
@@ -14096,7 +14096,7 @@
         </is>
       </c>
       <c r="E266" s="8" t="n">
-        <v>-9987090</v>
+        <v>-924449.88</v>
       </c>
       <c r="F266" s="8" t="n">
         <v>0</v>
@@ -14112,12 +14112,12 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>AC458</t>
+          <t>AC455</t>
         </is>
       </c>
       <c r="B267" s="6" t="inlineStr">
         <is>
-          <t>HAMZAOUI AMOKRANE</t>
+          <t>BENABAS FATEH</t>
         </is>
       </c>
       <c r="C267" s="7" t="inlineStr">
@@ -14131,7 +14131,7 @@
         </is>
       </c>
       <c r="E267" s="8" t="n">
-        <v>-1443600</v>
+        <v>-802905.91</v>
       </c>
       <c r="F267" s="8" t="n">
         <v>0</v>
@@ -14147,12 +14147,12 @@
     <row r="268">
       <c r="A268" s="7" t="inlineStr">
         <is>
-          <t>AC459</t>
+          <t>AC457</t>
         </is>
       </c>
       <c r="B268" s="6" t="inlineStr">
         <is>
-          <t>KASMI MOHAND</t>
+          <t>MESSAST ABDELOUAHAB</t>
         </is>
       </c>
       <c r="C268" s="7" t="inlineStr">
@@ -14166,7 +14166,7 @@
         </is>
       </c>
       <c r="E268" s="8" t="n">
-        <v>-564170</v>
+        <v>-9987090</v>
       </c>
       <c r="F268" s="8" t="n">
         <v>0</v>
@@ -14182,12 +14182,12 @@
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>AC460</t>
+          <t>AC458</t>
         </is>
       </c>
       <c r="B269" s="6" t="inlineStr">
         <is>
-          <t>MOHELLEBI MOHAMED</t>
+          <t>HAMZAOUI AMOKRANE</t>
         </is>
       </c>
       <c r="C269" s="7" t="inlineStr">
@@ -14201,7 +14201,7 @@
         </is>
       </c>
       <c r="E269" s="8" t="n">
-        <v>-593500</v>
+        <v>-1443600</v>
       </c>
       <c r="F269" s="8" t="n">
         <v>0</v>
@@ -14217,12 +14217,12 @@
     <row r="270">
       <c r="A270" s="7" t="inlineStr">
         <is>
-          <t>AC461</t>
+          <t>AC459</t>
         </is>
       </c>
       <c r="B270" s="6" t="inlineStr">
         <is>
-          <t>GUERBANE NASSIMA</t>
+          <t>KASMI MOHAND</t>
         </is>
       </c>
       <c r="C270" s="7" t="inlineStr">
@@ -14236,7 +14236,7 @@
         </is>
       </c>
       <c r="E270" s="8" t="n">
-        <v>-894116.15</v>
+        <v>-564170</v>
       </c>
       <c r="F270" s="8" t="n">
         <v>0</v>
@@ -14252,12 +14252,12 @@
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>AC462</t>
+          <t>AC460</t>
         </is>
       </c>
       <c r="B271" s="6" t="inlineStr">
         <is>
-          <t>CHEGRA MOULOUD</t>
+          <t>MOHELLEBI MOHAMED</t>
         </is>
       </c>
       <c r="C271" s="7" t="inlineStr">
@@ -14271,7 +14271,7 @@
         </is>
       </c>
       <c r="E271" s="8" t="n">
-        <v>-907634.41</v>
+        <v>-593500</v>
       </c>
       <c r="F271" s="8" t="n">
         <v>0</v>
@@ -14287,12 +14287,12 @@
     <row r="272">
       <c r="A272" s="7" t="inlineStr">
         <is>
-          <t>AC463</t>
+          <t>AC461</t>
         </is>
       </c>
       <c r="B272" s="6" t="inlineStr">
         <is>
-          <t>SNC LASMI ET CIE HYGIENNE</t>
+          <t>GUERBANE NASSIMA</t>
         </is>
       </c>
       <c r="C272" s="7" t="inlineStr">
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="E272" s="8" t="n">
-        <v>-4586600</v>
+        <v>-894116.15</v>
       </c>
       <c r="F272" s="8" t="n">
         <v>0</v>
@@ -14322,12 +14322,12 @@
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>AC466</t>
+          <t>AC462</t>
         </is>
       </c>
       <c r="B273" s="6" t="inlineStr">
         <is>
-          <t>SPA EPE SODISMAC</t>
+          <t>CHEGRA MOULOUD</t>
         </is>
       </c>
       <c r="C273" s="7" t="inlineStr">
@@ -14341,7 +14341,7 @@
         </is>
       </c>
       <c r="E273" s="8" t="n">
-        <v>-250000</v>
+        <v>-907634.41</v>
       </c>
       <c r="F273" s="8" t="n">
         <v>0</v>
@@ -14357,12 +14357,12 @@
     <row r="274">
       <c r="A274" s="7" t="inlineStr">
         <is>
-          <t>AC470</t>
+          <t>AC463</t>
         </is>
       </c>
       <c r="B274" s="6" t="inlineStr">
         <is>
-          <t>GHENABZIA BELKACEM</t>
+          <t>SNC LASMI ET CIE HYGIENNE</t>
         </is>
       </c>
       <c r="C274" s="7" t="inlineStr">
@@ -14376,7 +14376,7 @@
         </is>
       </c>
       <c r="E274" s="8" t="n">
-        <v>-185540</v>
+        <v>-4586600</v>
       </c>
       <c r="F274" s="8" t="n">
         <v>0</v>
@@ -14392,12 +14392,12 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>AC472</t>
+          <t>AC466</t>
         </is>
       </c>
       <c r="B275" s="6" t="inlineStr">
         <is>
-          <t>HALLABI AHMED</t>
+          <t>SPA EPE SODISMAC</t>
         </is>
       </c>
       <c r="C275" s="7" t="inlineStr">
@@ -14411,7 +14411,7 @@
         </is>
       </c>
       <c r="E275" s="8" t="n">
-        <v>-200000</v>
+        <v>-250000</v>
       </c>
       <c r="F275" s="8" t="n">
         <v>0</v>
@@ -14427,12 +14427,12 @@
     <row r="276">
       <c r="A276" s="7" t="inlineStr">
         <is>
-          <t>AC473</t>
+          <t>AC470</t>
         </is>
       </c>
       <c r="B276" s="6" t="inlineStr">
         <is>
-          <t>SNC MOTEUR BLEU ZIANI ET CIE</t>
+          <t>GHENABZIA BELKACEM</t>
         </is>
       </c>
       <c r="C276" s="7" t="inlineStr">
@@ -14446,7 +14446,7 @@
         </is>
       </c>
       <c r="E276" s="8" t="n">
-        <v>-1000000</v>
+        <v>-185540</v>
       </c>
       <c r="F276" s="8" t="n">
         <v>0</v>
@@ -14462,12 +14462,12 @@
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>AC474</t>
+          <t>AC472</t>
         </is>
       </c>
       <c r="B277" s="6" t="inlineStr">
         <is>
-          <t>REDJIMI EP SELAIMIA NOURELHOUD</t>
+          <t>HALLABI AHMED</t>
         </is>
       </c>
       <c r="C277" s="7" t="inlineStr">
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="E277" s="8" t="n">
-        <v>-1825600</v>
+        <v>-200000</v>
       </c>
       <c r="F277" s="8" t="n">
         <v>0</v>
@@ -14497,12 +14497,12 @@
     <row r="278">
       <c r="A278" s="7" t="inlineStr">
         <is>
-          <t>AC475</t>
+          <t>AC473</t>
         </is>
       </c>
       <c r="B278" s="6" t="inlineStr">
         <is>
-          <t>KADOUR AMAR</t>
+          <t>SNC MOTEUR BLEU ZIANI ET CIE</t>
         </is>
       </c>
       <c r="C278" s="7" t="inlineStr">
@@ -14516,7 +14516,7 @@
         </is>
       </c>
       <c r="E278" s="8" t="n">
-        <v>-240000</v>
+        <v>-1000000</v>
       </c>
       <c r="F278" s="8" t="n">
         <v>0</v>
@@ -14530,25 +14530,95 @@
       </c>
     </row>
     <row r="279">
-      <c r="B279" s="10" t="inlineStr">
+      <c r="A279" s="7" t="inlineStr">
+        <is>
+          <t>AC474</t>
+        </is>
+      </c>
+      <c r="B279" s="6" t="inlineStr">
+        <is>
+          <t>REDJIMI EP SELAIMIA NOURELHOUD</t>
+        </is>
+      </c>
+      <c r="C279" s="7" t="inlineStr">
+        <is>
+          <t>41900</t>
+        </is>
+      </c>
+      <c r="D279" s="6" t="inlineStr">
+        <is>
+          <t>Clients créditeurs -avances re</t>
+        </is>
+      </c>
+      <c r="E279" s="8" t="n">
+        <v>-1825600</v>
+      </c>
+      <c r="F279" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H279" s="8">
+        <f>E279+F279-G279</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="7" t="inlineStr">
+        <is>
+          <t>AC475</t>
+        </is>
+      </c>
+      <c r="B280" s="6" t="inlineStr">
+        <is>
+          <t>KADOUR AMAR</t>
+        </is>
+      </c>
+      <c r="C280" s="7" t="inlineStr">
+        <is>
+          <t>41900</t>
+        </is>
+      </c>
+      <c r="D280" s="6" t="inlineStr">
+        <is>
+          <t>Clients créditeurs -avances re</t>
+        </is>
+      </c>
+      <c r="E280" s="8" t="n">
+        <v>-240000</v>
+      </c>
+      <c r="F280" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" s="8">
+        <f>E280+F280-G280</f>
+        <v/>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E279" s="11">
-        <f>SUM(E4:E278)</f>
-        <v/>
-      </c>
-      <c r="F279" s="11">
-        <f>SUM(F4:F278)</f>
-        <v/>
-      </c>
-      <c r="G279" s="11">
-        <f>SUM(G4:G278)</f>
-        <v/>
-      </c>
-      <c r="H279" s="11">
-        <f>SUM(H4:H278)</f>
+      <c r="E281" s="11">
+        <f>SUM(E4:E280)</f>
+        <v/>
+      </c>
+      <c r="F281" s="11">
+        <f>SUM(F4:F280)</f>
+        <v/>
+      </c>
+      <c r="G281" s="11">
+        <f>SUM(G4:G280)</f>
+        <v/>
+      </c>
+      <c r="H281" s="11">
+        <f>SUM(H4:H280)</f>
         <v/>
       </c>
     </row>
